--- a/experiments/spatial_temporal_graph/experiment_metrics.xlsx
+++ b/experiments/spatial_temporal_graph/experiment_metrics.xlsx
@@ -24,13 +24,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +44,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -49,12 +52,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -442,77 +454,77 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>MaxTrials</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>N Folds/Subjects</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Acc Mean±SD</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Sens Mean±SD</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Spec Mean±SD</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Prec Mean±SD</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean±SD</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Overall Acc</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Overall Sens</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Overall Spec</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Overall Prec</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Overall F1</t>
         </is>
@@ -544,43 +556,43 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.758±0.104</t>
+          <t>0.749±0.125</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.897±0.069</t>
+          <t>0.900±0.137</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.645±0.192</t>
+          <t>0.631±0.213</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.703±0.144</t>
+          <t>0.694±0.149</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.779±0.085</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="n">
-        <v>0.7581</v>
-      </c>
-      <c r="L2" s="1" t="n">
+          <t>0.773±0.109</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>0.8966</v>
       </c>
-      <c r="M2" s="1" t="n">
-        <v>0.6364</v>
-      </c>
-      <c r="N2" s="1" t="n">
-        <v>0.6842</v>
-      </c>
-      <c r="O2" s="1" t="n">
-        <v>0.7761</v>
+      <c r="M2" s="2" t="n">
+        <v>0.6212</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0.6753</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.7704</v>
       </c>
     </row>
     <row r="3">
@@ -609,43 +621,43 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.712±0.089</t>
+          <t>0.733±0.077</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.907±0.079</t>
+          <t>0.880±0.052</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.548±0.159</t>
+          <t>0.608±0.151</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.645±0.097</t>
+          <t>0.672±0.102</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.748±0.067</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="n">
-        <v>0.7137</v>
-      </c>
-      <c r="L3" s="1" t="n">
-        <v>0.9052</v>
-      </c>
-      <c r="M3" s="1" t="n">
-        <v>0.5455</v>
-      </c>
-      <c r="N3" s="1" t="n">
-        <v>0.6364</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>0.7473</v>
+          <t>0.757±0.059</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0.7339</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0.8793</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0.6061</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.6623</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0.7556</v>
       </c>
     </row>
     <row r="4">
@@ -674,43 +686,43 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.740±0.130</t>
+          <t>0.741±0.128</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.950±0.075</t>
+          <t>0.930±0.071</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.560±0.297</t>
+          <t>0.581±0.252</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.684±0.157</t>
+          <t>0.684±0.163</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.782±0.083</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="n">
+          <t>0.777±0.097</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
         <v>0.7419</v>
       </c>
-      <c r="L4" s="1" t="n">
-        <v>0.9483</v>
-      </c>
-      <c r="M4" s="1" t="n">
-        <v>0.5606</v>
-      </c>
-      <c r="N4" s="1" t="n">
-        <v>0.6548</v>
-      </c>
-      <c r="O4" s="1" t="n">
-        <v>0.7746</v>
+      <c r="L4" s="2" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0.5758</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0.6585</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0.7714</v>
       </c>
     </row>
     <row r="5">
@@ -739,43 +751,43 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.749±0.088</t>
+          <t>0.692±0.087</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.905±0.080</t>
+          <t>0.932±0.055</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.618±0.112</t>
+          <t>0.486±0.124</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.677±0.093</t>
+          <t>0.617±0.079</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.771±0.079</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L5" s="1" t="n">
-        <v>0.9052</v>
-      </c>
-      <c r="M5" s="1" t="n">
+          <t>0.740±0.067</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0.6935</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0.4848</v>
+      </c>
+      <c r="N5" s="2" t="n">
         <v>0.6136</v>
       </c>
-      <c r="N5" s="1" t="n">
-        <v>0.6731</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>0.7721</v>
+      <c r="O5" s="2" t="n">
+        <v>0.7397</v>
       </c>
     </row>
     <row r="6">
@@ -804,43 +816,43 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.765±0.112</t>
+          <t>0.774±0.117</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.917±0.102</t>
+          <t>0.913±0.102</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.643±0.183</t>
+          <t>0.660±0.201</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.702±0.138</t>
+          <t>0.714±0.146</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.788±0.096</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>0.7661</v>
-      </c>
-      <c r="L6" s="1" t="n">
+          <t>0.794±0.102</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0.7742</v>
+      </c>
+      <c r="L6" s="2" t="n">
         <v>0.9137999999999999</v>
       </c>
-      <c r="M6" s="1" t="n">
-        <v>0.6364</v>
-      </c>
-      <c r="N6" s="1" t="n">
-        <v>0.6883</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <v>0.7852</v>
+      <c r="M6" s="2" t="n">
+        <v>0.6515</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0.6974</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0.791</v>
       </c>
     </row>
     <row r="7">
@@ -869,43 +881,43 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.704±0.089</t>
+          <t>0.712±0.112</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.873±0.140</t>
+          <t>0.900±0.081</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.564±0.172</t>
+          <t>0.558±0.240</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.646±0.095</t>
+          <t>0.661±0.140</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.733±0.077</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>0.7056</v>
-      </c>
-      <c r="L7" s="1" t="n">
-        <v>0.8707</v>
-      </c>
-      <c r="M7" s="1" t="n">
-        <v>0.5606</v>
-      </c>
-      <c r="N7" s="1" t="n">
-        <v>0.6352</v>
-      </c>
-      <c r="O7" s="1" t="n">
-        <v>0.7345</v>
+          <t>0.750±0.073</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0.7137</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0.8966</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0.7455000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -955,152 +967,152 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>MaxTrials</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>N Folds/Subjects</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Acc Mean</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Acc SD</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Acc Mean±SD</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Acc 95% CI</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Sens Mean</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Sens SD</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Sens Mean±SD</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Sens 95% CI</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Spec Mean</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Spec SD</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Spec Mean±SD</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Spec 95% CI</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Prec Mean</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Prec SD</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Prec Mean±SD</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Prec 95% CI</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 SD</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean±SD</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>F1 95% CI</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Overall Acc</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Overall Sens</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Overall Spec</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Overall Prec</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Overall F1</t>
         </is>
@@ -1130,100 +1142,100 @@
       <c r="E2" t="n">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="n">
-        <v>0.7577</v>
-      </c>
-      <c r="G2" s="1" t="n">
-        <v>0.1043</v>
+      <c r="F2" s="2" t="n">
+        <v>0.7494</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.1254</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.758±0.104</t>
+          <t>0.749±0.125</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[0.666, 0.849]</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>0.8967000000000001</v>
-      </c>
-      <c r="K2" s="1" t="n">
-        <v>0.06909999999999999</v>
+          <t>[0.639, 0.859]</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0.1369</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.897±0.069</t>
+          <t>0.900±0.137</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>[0.836, 0.957]</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="n">
-        <v>0.6452</v>
-      </c>
-      <c r="O2" s="1" t="n">
-        <v>0.1917</v>
+          <t>[0.780, 1.020]</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.2133</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.645±0.192</t>
+          <t>0.631±0.213</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[0.477, 0.813]</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="n">
-        <v>0.7028</v>
-      </c>
-      <c r="S2" s="1" t="n">
-        <v>0.1444</v>
+          <t>[0.444, 0.818]</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0.6942</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>0.1487</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.703±0.144</t>
+          <t>0.694±0.149</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>[0.576, 0.829]</t>
-        </is>
-      </c>
-      <c r="V2" s="1" t="n">
-        <v>0.7792</v>
-      </c>
-      <c r="W2" s="1" t="n">
-        <v>0.0853</v>
+          <t>[0.564, 0.824]</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>0.7727000000000001</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>0.109</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.779±0.085</t>
+          <t>0.773±0.109</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[0.704, 0.854]</t>
-        </is>
-      </c>
-      <c r="Z2" s="1" t="n">
-        <v>0.7581</v>
-      </c>
-      <c r="AA2" s="1" t="n">
+          <t>[0.677, 0.868]</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AA2" s="2" t="n">
         <v>0.8966</v>
       </c>
-      <c r="AB2" s="1" t="n">
-        <v>0.6364</v>
-      </c>
-      <c r="AC2" s="1" t="n">
-        <v>0.6842</v>
-      </c>
-      <c r="AD2" s="1" t="n">
-        <v>0.7761</v>
+      <c r="AB2" s="2" t="n">
+        <v>0.6212</v>
+      </c>
+      <c r="AC2" s="2" t="n">
+        <v>0.6753</v>
+      </c>
+      <c r="AD2" s="2" t="n">
+        <v>0.7704</v>
       </c>
     </row>
     <row r="3">
@@ -1250,100 +1262,100 @@
       <c r="E3" t="n">
         <v>5</v>
       </c>
-      <c r="F3" s="1" t="n">
-        <v>0.7122000000000001</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>0.0888</v>
+      <c r="F3" s="2" t="n">
+        <v>0.7327</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.07729999999999999</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.712±0.089</t>
+          <t>0.733±0.077</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[0.634, 0.790]</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>0.9067</v>
-      </c>
-      <c r="K3" s="1" t="n">
-        <v>0.0789</v>
+          <t>[0.665, 0.800]</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0.0522</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.907±0.079</t>
+          <t>0.880±0.052</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>[0.837, 0.976]</t>
-        </is>
-      </c>
-      <c r="N3" s="1" t="n">
-        <v>0.5476</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>0.1586</v>
+          <t>[0.834, 0.926]</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.6083</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0.1512</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.548±0.159</t>
+          <t>0.608±0.151</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>[0.409, 0.687]</t>
-        </is>
-      </c>
-      <c r="R3" s="1" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="S3" s="1" t="n">
-        <v>0.0975</v>
+          <t>[0.476, 0.741]</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0.6719000000000001</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>0.1022</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.645±0.097</t>
+          <t>0.672±0.102</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>[0.560, 0.730]</t>
-        </is>
-      </c>
-      <c r="V3" s="1" t="n">
-        <v>0.7484</v>
-      </c>
-      <c r="W3" s="1" t="n">
-        <v>0.0673</v>
+          <t>[0.582, 0.761]</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>0.7568</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>0.0593</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.748±0.067</t>
+          <t>0.757±0.059</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>[0.689, 0.807]</t>
-        </is>
-      </c>
-      <c r="Z3" s="1" t="n">
-        <v>0.7137</v>
-      </c>
-      <c r="AA3" s="1" t="n">
-        <v>0.9052</v>
-      </c>
-      <c r="AB3" s="1" t="n">
-        <v>0.5455</v>
-      </c>
-      <c r="AC3" s="1" t="n">
-        <v>0.6364</v>
-      </c>
-      <c r="AD3" s="1" t="n">
-        <v>0.7473</v>
+          <t>[0.705, 0.809]</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>0.7339</v>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v>0.8793</v>
+      </c>
+      <c r="AB3" s="2" t="n">
+        <v>0.6061</v>
+      </c>
+      <c r="AC3" s="2" t="n">
+        <v>0.6623</v>
+      </c>
+      <c r="AD3" s="2" t="n">
+        <v>0.7556</v>
       </c>
     </row>
     <row r="4">
@@ -1370,100 +1382,100 @@
       <c r="E4" t="n">
         <v>5</v>
       </c>
-      <c r="F4" s="1" t="n">
-        <v>0.7397</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>0.1305</v>
+      <c r="F4" s="2" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.1276</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.740±0.130</t>
+          <t>0.741±0.128</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[0.625, 0.854]</t>
-        </is>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="K4" s="1" t="n">
-        <v>0.0745</v>
+          <t>[0.629, 0.853]</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0.0711</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.950±0.075</t>
+          <t>0.930±0.071</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>[0.885, 1.015]</t>
-        </is>
-      </c>
-      <c r="N4" s="1" t="n">
-        <v>0.5595</v>
-      </c>
-      <c r="O4" s="1" t="n">
-        <v>0.2974</v>
+          <t>[0.868, 0.992]</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0.581</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0.2525</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.560±0.297</t>
+          <t>0.581±0.252</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>[0.299, 0.820]</t>
-        </is>
-      </c>
-      <c r="R4" s="1" t="n">
-        <v>0.6837</v>
-      </c>
-      <c r="S4" s="1" t="n">
-        <v>0.1574</v>
+          <t>[0.360, 0.802]</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0.6842</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>0.1628</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.684±0.157</t>
+          <t>0.684±0.163</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>[0.546, 0.822]</t>
-        </is>
-      </c>
-      <c r="V4" s="1" t="n">
-        <v>0.7816</v>
-      </c>
-      <c r="W4" s="1" t="n">
-        <v>0.08309999999999999</v>
+          <t>[0.542, 0.827]</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>0.7771</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>0.097</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.782±0.083</t>
+          <t>0.777±0.097</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>[0.709, 0.854]</t>
-        </is>
-      </c>
-      <c r="Z4" s="1" t="n">
+          <t>[0.692, 0.862]</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="n">
         <v>0.7419</v>
       </c>
-      <c r="AA4" s="1" t="n">
-        <v>0.9483</v>
-      </c>
-      <c r="AB4" s="1" t="n">
-        <v>0.5606</v>
-      </c>
-      <c r="AC4" s="1" t="n">
-        <v>0.6548</v>
-      </c>
-      <c r="AD4" s="1" t="n">
-        <v>0.7746</v>
+      <c r="AA4" s="2" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="AB4" s="2" t="n">
+        <v>0.5758</v>
+      </c>
+      <c r="AC4" s="2" t="n">
+        <v>0.6585</v>
+      </c>
+      <c r="AD4" s="2" t="n">
+        <v>0.7714</v>
       </c>
     </row>
     <row r="5">
@@ -1490,100 +1502,100 @@
       <c r="E5" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="1" t="n">
-        <v>0.7494</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>0.0878</v>
+      <c r="F5" s="2" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.0867</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.749±0.088</t>
+          <t>0.692±0.087</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[0.672, 0.826]</t>
-        </is>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>0.0801</v>
+          <t>[0.616, 0.768]</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0.9317</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0.0551</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.905±0.080</t>
+          <t>0.932±0.055</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>[0.835, 0.975]</t>
-        </is>
-      </c>
-      <c r="N5" s="1" t="n">
-        <v>0.6179</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>0.112</v>
+          <t>[0.883, 0.980]</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>0.4857</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0.1236</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.618±0.112</t>
+          <t>0.486±0.124</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>[0.520, 0.716]</t>
-        </is>
-      </c>
-      <c r="R5" s="1" t="n">
-        <v>0.6767</v>
-      </c>
-      <c r="S5" s="1" t="n">
-        <v>0.0934</v>
+          <t>[0.377, 0.594]</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0.6169</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>0.07920000000000001</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.677±0.093</t>
+          <t>0.617±0.079</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>[0.595, 0.759]</t>
-        </is>
-      </c>
-      <c r="V5" s="1" t="n">
-        <v>0.7715</v>
-      </c>
-      <c r="W5" s="1" t="n">
-        <v>0.0794</v>
+          <t>[0.547, 0.686]</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>0.7398</v>
+      </c>
+      <c r="W5" s="2" t="n">
+        <v>0.067</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.771±0.079</t>
+          <t>0.740±0.067</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>[0.702, 0.841]</t>
-        </is>
-      </c>
-      <c r="Z5" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AA5" s="1" t="n">
-        <v>0.9052</v>
-      </c>
-      <c r="AB5" s="1" t="n">
+          <t>[0.681, 0.798]</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>0.6935</v>
+      </c>
+      <c r="AA5" s="2" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="AB5" s="2" t="n">
+        <v>0.4848</v>
+      </c>
+      <c r="AC5" s="2" t="n">
         <v>0.6136</v>
       </c>
-      <c r="AC5" s="1" t="n">
-        <v>0.6731</v>
-      </c>
-      <c r="AD5" s="1" t="n">
-        <v>0.7721</v>
+      <c r="AD5" s="2" t="n">
+        <v>0.7397</v>
       </c>
     </row>
     <row r="6">
@@ -1610,100 +1622,100 @@
       <c r="E6" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="1" t="n">
-        <v>0.7654</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>0.1119</v>
+      <c r="F6" s="2" t="n">
+        <v>0.7737000000000001</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.1174</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.765±0.112</t>
+          <t>0.774±0.117</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[0.667, 0.863]</t>
-        </is>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>0.9167</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>0.1021</v>
+          <t>[0.671, 0.877]</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0.9133</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0.1023</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.917±0.102</t>
+          <t>0.913±0.102</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>[0.827, 1.006]</t>
-        </is>
-      </c>
-      <c r="N6" s="1" t="n">
-        <v>0.6429</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <v>0.1835</v>
+          <t>[0.824, 1.003]</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0.6595</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0.2006</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.643±0.183</t>
+          <t>0.660±0.201</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>[0.482, 0.804]</t>
-        </is>
-      </c>
-      <c r="R6" s="1" t="n">
-        <v>0.7024</v>
-      </c>
-      <c r="S6" s="1" t="n">
-        <v>0.1382</v>
+          <t>[0.484, 0.835]</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>0.1457</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0.702±0.138</t>
+          <t>0.714±0.146</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>[0.581, 0.824]</t>
-        </is>
-      </c>
-      <c r="V6" s="1" t="n">
-        <v>0.7877999999999999</v>
-      </c>
-      <c r="W6" s="1" t="n">
-        <v>0.0959</v>
+          <t>[0.587, 0.842]</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0.7936</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0.1022</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.788±0.096</t>
+          <t>0.794±0.102</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>[0.704, 0.872]</t>
-        </is>
-      </c>
-      <c r="Z6" s="1" t="n">
-        <v>0.7661</v>
-      </c>
-      <c r="AA6" s="1" t="n">
+          <t>[0.704, 0.883]</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>0.7742</v>
+      </c>
+      <c r="AA6" s="2" t="n">
         <v>0.9137999999999999</v>
       </c>
-      <c r="AB6" s="1" t="n">
-        <v>0.6364</v>
-      </c>
-      <c r="AC6" s="1" t="n">
-        <v>0.6883</v>
-      </c>
-      <c r="AD6" s="1" t="n">
-        <v>0.7852</v>
+      <c r="AB6" s="2" t="n">
+        <v>0.6515</v>
+      </c>
+      <c r="AC6" s="2" t="n">
+        <v>0.6974</v>
+      </c>
+      <c r="AD6" s="2" t="n">
+        <v>0.791</v>
       </c>
     </row>
     <row r="7">
@@ -1730,100 +1742,100 @@
       <c r="E7" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="1" t="n">
-        <v>0.7035</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>0.0891</v>
+      <c r="F7" s="2" t="n">
+        <v>0.7122000000000001</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.1125</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.704±0.089</t>
+          <t>0.712±0.112</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[0.625, 0.782]</t>
-        </is>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>0.8733</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>0.1401</v>
+          <t>[0.614, 0.811]</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0.08119999999999999</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.873±0.140</t>
+          <t>0.900±0.081</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>[0.751, 0.996]</t>
-        </is>
-      </c>
-      <c r="N7" s="1" t="n">
-        <v>0.5643</v>
-      </c>
-      <c r="O7" s="1" t="n">
-        <v>0.1724</v>
+          <t>[0.829, 0.971]</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0.5583</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0.2398</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.564±0.172</t>
+          <t>0.558±0.240</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>[0.413, 0.715]</t>
-        </is>
-      </c>
-      <c r="R7" s="1" t="n">
-        <v>0.6457000000000001</v>
-      </c>
-      <c r="S7" s="1" t="n">
-        <v>0.0953</v>
+          <t>[0.348, 0.769]</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0.6613</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>0.1403</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.646±0.095</t>
+          <t>0.661±0.140</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>[0.562, 0.729]</t>
-        </is>
-      </c>
-      <c r="V7" s="1" t="n">
-        <v>0.7327</v>
-      </c>
-      <c r="W7" s="1" t="n">
-        <v>0.0775</v>
+          <t>[0.538, 0.784]</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>0.7504</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0.0731</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.733±0.077</t>
+          <t>0.750±0.073</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>[0.665, 0.801]</t>
-        </is>
-      </c>
-      <c r="Z7" s="1" t="n">
-        <v>0.7056</v>
-      </c>
-      <c r="AA7" s="1" t="n">
-        <v>0.8707</v>
-      </c>
-      <c r="AB7" s="1" t="n">
-        <v>0.5606</v>
-      </c>
-      <c r="AC7" s="1" t="n">
-        <v>0.6352</v>
-      </c>
-      <c r="AD7" s="1" t="n">
-        <v>0.7345</v>
+          <t>[0.686, 0.815]</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>0.7137</v>
+      </c>
+      <c r="AA7" s="2" t="n">
+        <v>0.8966</v>
+      </c>
+      <c r="AB7" s="2" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="AC7" s="2" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="AD7" s="2" t="n">
+        <v>0.7455000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1858,77 +1870,77 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>MaxTrials</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>N Folds/Subjects</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Acc Mean±SD</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Sens Mean±SD</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Spec Mean±SD</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Prec Mean±SD</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean±SD</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Overall Acc</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Overall Sens</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Overall Spec</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Overall Prec</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Overall F1</t>
         </is>
@@ -1960,43 +1972,43 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.781±0.132</t>
+          <t>0.764±0.146</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.933±0.086</t>
+          <t>0.942±0.097</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.650±0.281</t>
+          <t>0.592±0.304</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.730±0.156</t>
+          <t>0.705±0.138</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.806±0.096</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="n">
-        <v>0.7823</v>
-      </c>
-      <c r="L2" s="1" t="n">
-        <v>0.931</v>
-      </c>
-      <c r="M2" s="1" t="n">
-        <v>0.6515</v>
-      </c>
-      <c r="N2" s="1" t="n">
-        <v>0.7013</v>
-      </c>
-      <c r="O2" s="1" t="n">
-        <v>0.8</v>
+          <t>0.798±0.098</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0.7661</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0.9483</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0.6061</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.7914</v>
       </c>
     </row>
     <row r="3">
@@ -2025,43 +2037,43 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.747±0.114</t>
+          <t>0.749±0.129</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.904±0.108</t>
+          <t>0.908±0.083</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.596±0.231</t>
+          <t>0.592±0.279</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.685±0.093</t>
+          <t>0.699±0.127</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.775±0.080</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="n">
+          <t>0.781±0.078</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
         <v>0.75</v>
       </c>
-      <c r="L3" s="1" t="n">
-        <v>0.9052</v>
-      </c>
-      <c r="M3" s="1" t="n">
-        <v>0.6136</v>
-      </c>
-      <c r="N3" s="1" t="n">
-        <v>0.6731</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>0.7721</v>
+      <c r="L3" s="2" t="n">
+        <v>0.9137999999999999</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0.6061</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.6709000000000001</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0.7737000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -2090,43 +2102,43 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.756±0.133</t>
+          <t>0.764±0.135</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.950±0.112</t>
+          <t>0.933±0.086</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.583±0.288</t>
+          <t>0.608±0.275</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.700±0.153</t>
+          <t>0.703±0.121</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.791±0.087</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="n">
-        <v>0.7581</v>
-      </c>
-      <c r="L4" s="1" t="n">
-        <v>0.9483</v>
-      </c>
-      <c r="M4" s="1" t="n">
-        <v>0.5909</v>
-      </c>
-      <c r="N4" s="1" t="n">
-        <v>0.6707</v>
-      </c>
-      <c r="O4" s="1" t="n">
-        <v>0.7857</v>
+          <t>0.795±0.088</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0.7661</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0.6212</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0.6835</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0.7883</v>
       </c>
     </row>
     <row r="5">
@@ -2155,43 +2167,43 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.752±0.125</t>
+          <t>0.736±0.133</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.925±0.100</t>
+          <t>0.929±0.056</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.579±0.305</t>
+          <t>0.556±0.258</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.706±0.133</t>
+          <t>0.671±0.105</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.787±0.070</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>0.754</v>
-      </c>
-      <c r="L5" s="1" t="n">
+          <t>0.775±0.080</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0.7379</v>
+      </c>
+      <c r="L5" s="2" t="n">
         <v>0.931</v>
       </c>
-      <c r="M5" s="1" t="n">
-        <v>0.5985</v>
-      </c>
-      <c r="N5" s="1" t="n">
-        <v>0.6708</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>0.7798</v>
+      <c r="M5" s="2" t="n">
+        <v>0.5682</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>0.6545</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0.7687</v>
       </c>
     </row>
     <row r="6">
@@ -2220,43 +2232,43 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.796±0.132</t>
+          <t>0.771±0.167</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.917±0.142</t>
+          <t>0.933±0.117</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.692±0.281</t>
+          <t>0.625±0.348</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.758±0.146</t>
+          <t>0.736±0.184</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.813±0.093</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>0.7984</v>
-      </c>
-      <c r="L6" s="1" t="n">
-        <v>0.9137999999999999</v>
-      </c>
-      <c r="M6" s="1" t="n">
-        <v>0.697</v>
-      </c>
-      <c r="N6" s="1" t="n">
-        <v>0.726</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <v>0.8092</v>
+          <t>0.805±0.113</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0.7742</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0.6364</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0.6923</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0.7941</v>
       </c>
     </row>
     <row r="7">
@@ -2285,43 +2297,43 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.757±0.122</t>
+          <t>0.740±0.146</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.892±0.125</t>
+          <t>0.888±0.068</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.625±0.290</t>
+          <t>0.594±0.299</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.720±0.129</t>
+          <t>0.701±0.135</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.782±0.071</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>0.7581</v>
-      </c>
-      <c r="L7" s="1" t="n">
-        <v>0.8966</v>
-      </c>
-      <c r="M7" s="1" t="n">
-        <v>0.6364</v>
-      </c>
-      <c r="N7" s="1" t="n">
-        <v>0.6842</v>
-      </c>
-      <c r="O7" s="1" t="n">
-        <v>0.7761</v>
+          <t>0.775±0.089</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0.7419</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0.8879</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0.6136</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0.6688</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0.763</v>
       </c>
     </row>
   </sheetData>
@@ -2371,152 +2383,152 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>MaxTrials</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>N Folds/Subjects</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Acc Mean</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Acc SD</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Acc Mean±SD</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Acc 95% CI</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Sens Mean</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Sens SD</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Sens Mean±SD</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Sens 95% CI</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Spec Mean</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Spec SD</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Spec Mean±SD</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Spec 95% CI</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Prec Mean</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Prec SD</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Prec Mean±SD</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Prec 95% CI</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 SD</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean±SD</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>F1 95% CI</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Overall Acc</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Overall Sens</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Overall Spec</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Overall Prec</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Overall F1</t>
         </is>
@@ -2546,100 +2558,100 @@
       <c r="E2" t="n">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="n">
-        <v>0.781</v>
-      </c>
-      <c r="G2" s="1" t="n">
-        <v>0.1316</v>
+      <c r="F2" s="2" t="n">
+        <v>0.7643</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.1458</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.781±0.132</t>
+          <t>0.764±0.146</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[0.699, 0.863]</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>0.9333</v>
-      </c>
-      <c r="K2" s="1" t="n">
-        <v>0.0861</v>
+          <t>[0.674, 0.855]</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0.9417</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0.09660000000000001</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.933±0.086</t>
+          <t>0.942±0.097</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>[0.880, 0.987]</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="O2" s="1" t="n">
-        <v>0.2807</v>
+          <t>[0.882, 1.002]</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0.5917</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.3035</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.650±0.281</t>
+          <t>0.592±0.304</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[0.476, 0.824]</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="n">
-        <v>0.7298</v>
-      </c>
-      <c r="S2" s="1" t="n">
-        <v>0.1561</v>
+          <t>[0.404, 0.780]</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0.7050999999999999</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>0.1377</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.730±0.156</t>
+          <t>0.705±0.138</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>[0.633, 0.827]</t>
-        </is>
-      </c>
-      <c r="V2" s="1" t="n">
-        <v>0.806</v>
-      </c>
-      <c r="W2" s="1" t="n">
-        <v>0.0959</v>
+          <t>[0.620, 0.790]</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>0.7977</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>0.0984</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.806±0.096</t>
+          <t>0.798±0.098</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[0.747, 0.865]</t>
-        </is>
-      </c>
-      <c r="Z2" s="1" t="n">
-        <v>0.7823</v>
-      </c>
-      <c r="AA2" s="1" t="n">
-        <v>0.931</v>
-      </c>
-      <c r="AB2" s="1" t="n">
-        <v>0.6515</v>
-      </c>
-      <c r="AC2" s="1" t="n">
-        <v>0.7013</v>
-      </c>
-      <c r="AD2" s="1" t="n">
-        <v>0.8</v>
+          <t>[0.737, 0.859]</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="n">
+        <v>0.7661</v>
+      </c>
+      <c r="AA2" s="2" t="n">
+        <v>0.9483</v>
+      </c>
+      <c r="AB2" s="2" t="n">
+        <v>0.6061</v>
+      </c>
+      <c r="AC2" s="2" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="AD2" s="2" t="n">
+        <v>0.7914</v>
       </c>
     </row>
     <row r="3">
@@ -2666,100 +2678,100 @@
       <c r="E3" t="n">
         <v>10</v>
       </c>
-      <c r="F3" s="1" t="n">
-        <v>0.747</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>0.114</v>
+      <c r="F3" s="2" t="n">
+        <v>0.7494</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.1286</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.747±0.114</t>
+          <t>0.749±0.129</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[0.676, 0.818]</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>0.9042</v>
-      </c>
-      <c r="K3" s="1" t="n">
-        <v>0.1077</v>
+          <t>[0.670, 0.829]</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0.9083</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0.0829</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.904±0.108</t>
+          <t>0.908±0.083</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>[0.837, 0.971]</t>
-        </is>
-      </c>
-      <c r="N3" s="1" t="n">
-        <v>0.5958</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>0.231</v>
+          <t>[0.857, 0.960]</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.5917</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0.2789</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.596±0.231</t>
+          <t>0.592±0.279</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>[0.453, 0.739]</t>
-        </is>
-      </c>
-      <c r="R3" s="1" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="S3" s="1" t="n">
-        <v>0.0929</v>
+          <t>[0.419, 0.765]</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0.6991000000000001</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>0.1272</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.685±0.093</t>
+          <t>0.699±0.127</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>[0.627, 0.743]</t>
-        </is>
-      </c>
-      <c r="V3" s="1" t="n">
-        <v>0.7745</v>
-      </c>
-      <c r="W3" s="1" t="n">
-        <v>0.08019999999999999</v>
+          <t>[0.620, 0.778]</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>0.0784</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.775±0.080</t>
+          <t>0.781±0.078</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>[0.725, 0.824]</t>
-        </is>
-      </c>
-      <c r="Z3" s="1" t="n">
+          <t>[0.732, 0.830]</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="n">
         <v>0.75</v>
       </c>
-      <c r="AA3" s="1" t="n">
-        <v>0.9052</v>
-      </c>
-      <c r="AB3" s="1" t="n">
-        <v>0.6136</v>
-      </c>
-      <c r="AC3" s="1" t="n">
-        <v>0.6731</v>
-      </c>
-      <c r="AD3" s="1" t="n">
-        <v>0.7721</v>
+      <c r="AA3" s="2" t="n">
+        <v>0.9137999999999999</v>
+      </c>
+      <c r="AB3" s="2" t="n">
+        <v>0.6061</v>
+      </c>
+      <c r="AC3" s="2" t="n">
+        <v>0.6709000000000001</v>
+      </c>
+      <c r="AD3" s="2" t="n">
+        <v>0.7737000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -2786,100 +2798,100 @@
       <c r="E4" t="n">
         <v>10</v>
       </c>
-      <c r="F4" s="1" t="n">
-        <v>0.756</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>0.1326</v>
+      <c r="F4" s="2" t="n">
+        <v>0.7643</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.1348</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.756±0.133</t>
+          <t>0.764±0.135</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[0.674, 0.838]</t>
-        </is>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="K4" s="1" t="n">
-        <v>0.1125</v>
+          <t>[0.681, 0.848]</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0.9333</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0.0861</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.950±0.112</t>
+          <t>0.933±0.086</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>[0.880, 1.020]</t>
-        </is>
-      </c>
-      <c r="N4" s="1" t="n">
-        <v>0.5833</v>
-      </c>
-      <c r="O4" s="1" t="n">
-        <v>0.288</v>
+          <t>[0.880, 0.987]</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0.6083</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0.2751</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.583±0.288</t>
+          <t>0.608±0.275</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>[0.405, 0.762]</t>
-        </is>
-      </c>
-      <c r="R4" s="1" t="n">
-        <v>0.7000999999999999</v>
-      </c>
-      <c r="S4" s="1" t="n">
-        <v>0.153</v>
+          <t>[0.438, 0.779]</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0.7029</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>0.1212</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.700±0.153</t>
+          <t>0.703±0.121</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>[0.605, 0.795]</t>
-        </is>
-      </c>
-      <c r="V4" s="1" t="n">
-        <v>0.7905</v>
-      </c>
-      <c r="W4" s="1" t="n">
-        <v>0.08649999999999999</v>
+          <t>[0.628, 0.778]</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>0.7951</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>0.08840000000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.791±0.087</t>
+          <t>0.795±0.088</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>[0.737, 0.844]</t>
-        </is>
-      </c>
-      <c r="Z4" s="1" t="n">
-        <v>0.7581</v>
-      </c>
-      <c r="AA4" s="1" t="n">
-        <v>0.9483</v>
-      </c>
-      <c r="AB4" s="1" t="n">
-        <v>0.5909</v>
-      </c>
-      <c r="AC4" s="1" t="n">
-        <v>0.6707</v>
-      </c>
-      <c r="AD4" s="1" t="n">
-        <v>0.7857</v>
+          <t>[0.740, 0.850]</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>0.7661</v>
+      </c>
+      <c r="AA4" s="2" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="AB4" s="2" t="n">
+        <v>0.6212</v>
+      </c>
+      <c r="AC4" s="2" t="n">
+        <v>0.6835</v>
+      </c>
+      <c r="AD4" s="2" t="n">
+        <v>0.7883</v>
       </c>
     </row>
     <row r="5">
@@ -2906,100 +2918,100 @@
       <c r="E5" t="n">
         <v>10</v>
       </c>
-      <c r="F5" s="1" t="n">
-        <v>0.7524</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>0.1246</v>
+      <c r="F5" s="2" t="n">
+        <v>0.7363</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.1327</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.752±0.125</t>
+          <t>0.736±0.133</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[0.675, 0.830]</t>
-        </is>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>0.0998</v>
+          <t>[0.654, 0.819]</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0.9292</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0.0557</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.925±0.100</t>
+          <t>0.929±0.056</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>[0.863, 0.987]</t>
-        </is>
-      </c>
-      <c r="N5" s="1" t="n">
-        <v>0.5792</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>0.3047</v>
+          <t>[0.895, 0.964]</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>0.5563</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0.2584</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.579±0.305</t>
+          <t>0.556±0.258</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>[0.390, 0.768]</t>
-        </is>
-      </c>
-      <c r="R5" s="1" t="n">
-        <v>0.7063</v>
-      </c>
-      <c r="S5" s="1" t="n">
-        <v>0.1326</v>
+          <t>[0.396, 0.716]</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0.6712</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>0.1048</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.706±0.133</t>
+          <t>0.671±0.105</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>[0.624, 0.788]</t>
-        </is>
-      </c>
-      <c r="V5" s="1" t="n">
-        <v>0.7875</v>
-      </c>
-      <c r="W5" s="1" t="n">
-        <v>0.0697</v>
+          <t>[0.606, 0.736]</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="W5" s="2" t="n">
+        <v>0.07969999999999999</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.787±0.070</t>
+          <t>0.775±0.080</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>[0.744, 0.831]</t>
-        </is>
-      </c>
-      <c r="Z5" s="1" t="n">
-        <v>0.754</v>
-      </c>
-      <c r="AA5" s="1" t="n">
+          <t>[0.726, 0.824]</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>0.7379</v>
+      </c>
+      <c r="AA5" s="2" t="n">
         <v>0.931</v>
       </c>
-      <c r="AB5" s="1" t="n">
-        <v>0.5985</v>
-      </c>
-      <c r="AC5" s="1" t="n">
-        <v>0.6708</v>
-      </c>
-      <c r="AD5" s="1" t="n">
-        <v>0.7798</v>
+      <c r="AB5" s="2" t="n">
+        <v>0.5682</v>
+      </c>
+      <c r="AC5" s="2" t="n">
+        <v>0.6545</v>
+      </c>
+      <c r="AD5" s="2" t="n">
+        <v>0.7687</v>
       </c>
     </row>
     <row r="6">
@@ -3026,100 +3038,100 @@
       <c r="E6" t="n">
         <v>10</v>
       </c>
-      <c r="F6" s="1" t="n">
-        <v>0.7964</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>0.1323</v>
+      <c r="F6" s="2" t="n">
+        <v>0.7714</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.1669</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.796±0.132</t>
+          <t>0.771±0.167</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[0.714, 0.878]</t>
-        </is>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>0.9167</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>0.1416</v>
+          <t>[0.668, 0.875]</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0.9333</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0.1165</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.917±0.142</t>
+          <t>0.933±0.117</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>[0.829, 1.004]</t>
-        </is>
-      </c>
-      <c r="N6" s="1" t="n">
-        <v>0.6917</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <v>0.2814</v>
+          <t>[0.861, 1.006]</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0.3481</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.692±0.281</t>
+          <t>0.625±0.348</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>[0.517, 0.866]</t>
-        </is>
-      </c>
-      <c r="R6" s="1" t="n">
-        <v>0.758</v>
-      </c>
-      <c r="S6" s="1" t="n">
-        <v>0.1456</v>
+          <t>[0.409, 0.841]</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0.7363</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>0.1836</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0.758±0.146</t>
+          <t>0.736±0.184</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>[0.668, 0.848]</t>
-        </is>
-      </c>
-      <c r="V6" s="1" t="n">
-        <v>0.8135</v>
-      </c>
-      <c r="W6" s="1" t="n">
-        <v>0.0927</v>
+          <t>[0.622, 0.850]</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0.8055</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0.1132</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.813±0.093</t>
+          <t>0.805±0.113</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>[0.756, 0.871]</t>
-        </is>
-      </c>
-      <c r="Z6" s="1" t="n">
-        <v>0.7984</v>
-      </c>
-      <c r="AA6" s="1" t="n">
-        <v>0.9137999999999999</v>
-      </c>
-      <c r="AB6" s="1" t="n">
-        <v>0.697</v>
-      </c>
-      <c r="AC6" s="1" t="n">
-        <v>0.726</v>
-      </c>
-      <c r="AD6" s="1" t="n">
-        <v>0.8092</v>
+          <t>[0.735, 0.876]</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>0.7742</v>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="AB6" s="2" t="n">
+        <v>0.6364</v>
+      </c>
+      <c r="AC6" s="2" t="n">
+        <v>0.6923</v>
+      </c>
+      <c r="AD6" s="2" t="n">
+        <v>0.7941</v>
       </c>
     </row>
     <row r="7">
@@ -3146,100 +3158,100 @@
       <c r="E7" t="n">
         <v>10</v>
       </c>
-      <c r="F7" s="1" t="n">
-        <v>0.7571</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>0.1219</v>
+      <c r="F7" s="2" t="n">
+        <v>0.7399</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.1463</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.757±0.122</t>
+          <t>0.740±0.146</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[0.682, 0.833]</t>
-        </is>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>0.8917</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>0.1245</v>
+          <t>[0.649, 0.831]</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.8875</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0.0682</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.892±0.125</t>
+          <t>0.888±0.068</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>[0.814, 0.969]</t>
-        </is>
-      </c>
-      <c r="N7" s="1" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="O7" s="1" t="n">
-        <v>0.2895</v>
+          <t>[0.845, 0.930]</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0.5938</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0.2992</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.625±0.290</t>
+          <t>0.594±0.299</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>[0.446, 0.804]</t>
-        </is>
-      </c>
-      <c r="R7" s="1" t="n">
-        <v>0.7201</v>
-      </c>
-      <c r="S7" s="1" t="n">
-        <v>0.1294</v>
+          <t>[0.408, 0.779]</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0.7005</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>0.1349</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.720±0.129</t>
+          <t>0.701±0.135</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>[0.640, 0.800]</t>
-        </is>
-      </c>
-      <c r="V7" s="1" t="n">
-        <v>0.7816</v>
-      </c>
-      <c r="W7" s="1" t="n">
-        <v>0.0706</v>
+          <t>[0.617, 0.784]</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>0.7746</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0.0886</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.782±0.071</t>
+          <t>0.775±0.089</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>[0.738, 0.825]</t>
-        </is>
-      </c>
-      <c r="Z7" s="1" t="n">
-        <v>0.7581</v>
-      </c>
-      <c r="AA7" s="1" t="n">
-        <v>0.8966</v>
-      </c>
-      <c r="AB7" s="1" t="n">
-        <v>0.6364</v>
-      </c>
-      <c r="AC7" s="1" t="n">
-        <v>0.6842</v>
-      </c>
-      <c r="AD7" s="1" t="n">
-        <v>0.7761</v>
+          <t>[0.720, 0.830]</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>0.7419</v>
+      </c>
+      <c r="AA7" s="2" t="n">
+        <v>0.8879</v>
+      </c>
+      <c r="AB7" s="2" t="n">
+        <v>0.6136</v>
+      </c>
+      <c r="AC7" s="2" t="n">
+        <v>0.6688</v>
+      </c>
+      <c r="AD7" s="2" t="n">
+        <v>0.763</v>
       </c>
     </row>
   </sheetData>
@@ -3274,77 +3286,77 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>MaxTrials</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>N Folds/Subjects</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Acc Mean±SD</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Sens Mean±SD</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Spec Mean±SD</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Prec Mean±SD</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean±SD</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Overall Acc</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Overall Sens</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Overall Spec</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Overall Prec</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Overall F1</t>
         </is>
@@ -3376,17 +3388,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.710±0.449</t>
+          <t>0.790±0.379</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.460±0.498</t>
+          <t>0.468±0.503</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.250±0.432</t>
+          <t>0.323±0.444</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -3396,23 +3408,23 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.462±0.499</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="n">
-        <v>0.7097</v>
-      </c>
-      <c r="L2" s="1" t="n">
-        <v>0.9828</v>
-      </c>
-      <c r="M2" s="1" t="n">
-        <v>0.4697</v>
-      </c>
-      <c r="N2" s="1" t="n">
-        <v>0.6196</v>
-      </c>
-      <c r="O2" s="1" t="n">
-        <v>0.76</v>
+          <t>0.468±0.503</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0.7903</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0.6061</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0.6905</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.8169</v>
       </c>
     </row>
     <row r="3">
@@ -3441,43 +3453,43 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.722±0.437</t>
+          <t>0.770±0.363</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>0.464±0.500</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.306±0.413</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.468±0.503</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.254±0.423</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.468±0.503</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.468±0.503</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="n">
-        <v>0.7218</v>
-      </c>
-      <c r="L3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" s="1" t="n">
-        <v>0.4773</v>
-      </c>
-      <c r="N3" s="1" t="n">
-        <v>0.627</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>0.7708</v>
+          <t>0.465±0.501</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0.7702</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0.9913999999999999</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0.5758</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.6725</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0.8014</v>
       </c>
     </row>
     <row r="4">
@@ -3506,7 +3518,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.726±0.441</t>
+          <t>0.823±0.340</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3516,7 +3528,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.258±0.432</t>
+          <t>0.355±0.447</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -3529,20 +3541,20 @@
           <t>0.468±0.503</t>
         </is>
       </c>
-      <c r="K4" s="1" t="n">
-        <v>0.7258</v>
-      </c>
-      <c r="L4" s="1" t="n">
+      <c r="K4" s="2" t="n">
+        <v>0.8226</v>
+      </c>
+      <c r="L4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M4" s="1" t="n">
-        <v>0.4848</v>
-      </c>
-      <c r="N4" s="1" t="n">
-        <v>0.6304</v>
-      </c>
-      <c r="O4" s="1" t="n">
-        <v>0.7733</v>
+      <c r="M4" s="2" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0.8406</v>
       </c>
     </row>
     <row r="5">
@@ -3571,17 +3583,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.746±0.428</t>
+          <t>0.815±0.297</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.460±0.496</t>
+          <t>0.464±0.500</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.286±0.452</t>
+          <t>0.351±0.411</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -3591,23 +3603,23 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.463±0.499</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>0.746</v>
-      </c>
-      <c r="L5" s="1" t="n">
-        <v>0.9828</v>
-      </c>
-      <c r="M5" s="1" t="n">
-        <v>0.5379</v>
-      </c>
-      <c r="N5" s="1" t="n">
-        <v>0.6514</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>0.7835</v>
+          <t>0.465±0.501</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0.8145</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0.9913999999999999</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0.6591</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>0.7188</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0.8333</v>
       </c>
     </row>
     <row r="6">
@@ -3636,7 +3648,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.766±0.412</t>
+          <t>0.782±0.391</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3646,7 +3658,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.298±0.448</t>
+          <t>0.315±0.446</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -3659,20 +3671,20 @@
           <t>0.468±0.503</t>
         </is>
       </c>
-      <c r="K6" s="1" t="n">
-        <v>0.7661</v>
-      </c>
-      <c r="L6" s="1" t="n">
+      <c r="K6" s="2" t="n">
+        <v>0.7823</v>
+      </c>
+      <c r="L6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M6" s="1" t="n">
-        <v>0.5606</v>
-      </c>
-      <c r="N6" s="1" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <v>0.8</v>
+      <c r="M6" s="2" t="n">
+        <v>0.5909</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0.6824</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0.8112</v>
       </c>
     </row>
     <row r="7">
@@ -3701,17 +3713,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.738±0.433</t>
+          <t>0.754±0.352</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.464±0.500</t>
+          <t>0.452±0.491</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.274±0.443</t>
+          <t>0.302±0.400</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3721,23 +3733,23 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.465±0.501</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>0.7379</v>
-      </c>
-      <c r="L7" s="1" t="n">
-        <v>0.9913999999999999</v>
-      </c>
-      <c r="M7" s="1" t="n">
-        <v>0.5152</v>
-      </c>
-      <c r="N7" s="1" t="n">
-        <v>0.6425</v>
-      </c>
-      <c r="O7" s="1" t="n">
-        <v>0.7796999999999999</v>
+          <t>0.458±0.495</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0.9655</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0.5682</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0.6627</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0.786</v>
       </c>
     </row>
   </sheetData>
@@ -3787,152 +3799,152 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>MaxTrials</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>N Folds/Subjects</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Acc Mean</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Acc SD</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Acc Mean±SD</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Acc 95% CI</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Sens Mean</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Sens SD</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Sens Mean±SD</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Sens 95% CI</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Spec Mean</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Spec SD</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Spec Mean±SD</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Spec 95% CI</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Prec Mean</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Prec SD</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Prec Mean±SD</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Prec 95% CI</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 SD</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean±SD</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>F1 95% CI</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Overall Acc</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Overall Sens</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Overall Spec</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Overall Prec</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Overall F1</t>
         </is>
@@ -3962,58 +3974,58 @@
       <c r="E2" t="n">
         <v>62</v>
       </c>
-      <c r="F2" s="1" t="n">
-        <v>0.7097</v>
-      </c>
-      <c r="G2" s="1" t="n">
-        <v>0.4486</v>
+      <c r="F2" s="2" t="n">
+        <v>0.7903</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.3793</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.710±0.449</t>
+          <t>0.790±0.379</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[0.598, 0.821]</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>0.4597</v>
-      </c>
-      <c r="K2" s="1" t="n">
-        <v>0.4983</v>
+          <t>[0.696, 0.885]</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0.4677</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0.503</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.460±0.498</t>
+          <t>0.468±0.503</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>[0.336, 0.584]</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O2" s="1" t="n">
-        <v>0.4318</v>
+          <t>[0.343, 0.593]</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.4444</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.250±0.432</t>
+          <t>0.323±0.444</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[0.143, 0.357]</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="n">
+          <t>[0.212, 0.433]</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="S2" s="1" t="n">
+      <c r="S2" s="2" t="n">
         <v>0.503</v>
       </c>
       <c r="T2" t="inlineStr">
@@ -4026,36 +4038,36 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="V2" s="1" t="n">
-        <v>0.4624</v>
-      </c>
-      <c r="W2" s="1" t="n">
-        <v>0.499</v>
+      <c r="V2" s="2" t="n">
+        <v>0.4677</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>0.503</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.462±0.499</t>
+          <t>0.468±0.503</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[0.338, 0.587]</t>
-        </is>
-      </c>
-      <c r="Z2" s="1" t="n">
-        <v>0.7097</v>
-      </c>
-      <c r="AA2" s="1" t="n">
-        <v>0.9828</v>
-      </c>
-      <c r="AB2" s="1" t="n">
-        <v>0.4697</v>
-      </c>
-      <c r="AC2" s="1" t="n">
-        <v>0.6196</v>
-      </c>
-      <c r="AD2" s="1" t="n">
-        <v>0.76</v>
+          <t>[0.343, 0.593]</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="n">
+        <v>0.7903</v>
+      </c>
+      <c r="AA2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="2" t="n">
+        <v>0.6061</v>
+      </c>
+      <c r="AC2" s="2" t="n">
+        <v>0.6905</v>
+      </c>
+      <c r="AD2" s="2" t="n">
+        <v>0.8169</v>
       </c>
     </row>
     <row r="3">
@@ -4082,100 +4094,100 @@
       <c r="E3" t="n">
         <v>62</v>
       </c>
-      <c r="F3" s="1" t="n">
-        <v>0.7218</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>0.4368</v>
+      <c r="F3" s="2" t="n">
+        <v>0.7702</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.363</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.722±0.437</t>
+          <t>0.770±0.363</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[0.613, 0.831]</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="n">
+          <t>[0.680, 0.861]</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0.4637</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0.4997</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.464±0.500</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>[0.339, 0.588]</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0.4135</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0.306±0.413</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>[0.204, 0.409]</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="K3" s="1" t="n">
+      <c r="S3" s="2" t="n">
         <v>0.503</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>0.468±0.503</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="N3" s="1" t="n">
-        <v>0.254</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>0.4234</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0.254±0.423</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>[0.149, 0.359]</t>
-        </is>
-      </c>
-      <c r="R3" s="1" t="n">
-        <v>0.4677</v>
-      </c>
-      <c r="S3" s="1" t="n">
-        <v>0.503</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>0.468±0.503</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>[0.343, 0.593]</t>
-        </is>
-      </c>
-      <c r="V3" s="1" t="n">
-        <v>0.4677</v>
-      </c>
-      <c r="W3" s="1" t="n">
-        <v>0.503</v>
+      <c r="V3" s="2" t="n">
+        <v>0.4654</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>0.5009</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.468±0.503</t>
+          <t>0.465±0.501</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>[0.343, 0.593]</t>
-        </is>
-      </c>
-      <c r="Z3" s="1" t="n">
-        <v>0.7218</v>
-      </c>
-      <c r="AA3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB3" s="1" t="n">
-        <v>0.4773</v>
-      </c>
-      <c r="AC3" s="1" t="n">
-        <v>0.627</v>
-      </c>
-      <c r="AD3" s="1" t="n">
-        <v>0.7708</v>
+          <t>[0.341, 0.590]</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>0.7702</v>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v>0.9913999999999999</v>
+      </c>
+      <c r="AB3" s="2" t="n">
+        <v>0.5758</v>
+      </c>
+      <c r="AC3" s="2" t="n">
+        <v>0.6725</v>
+      </c>
+      <c r="AD3" s="2" t="n">
+        <v>0.8014</v>
       </c>
     </row>
     <row r="4">
@@ -4202,26 +4214,26 @@
       <c r="E4" t="n">
         <v>62</v>
       </c>
-      <c r="F4" s="1" t="n">
-        <v>0.7258</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>0.4405</v>
+      <c r="F4" s="2" t="n">
+        <v>0.8226</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.3399</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.726±0.441</t>
+          <t>0.823±0.340</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[0.616, 0.835]</t>
-        </is>
-      </c>
-      <c r="J4" s="1" t="n">
+          <t>[0.738, 0.907]</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="K4" s="1" t="n">
+      <c r="K4" s="2" t="n">
         <v>0.503</v>
       </c>
       <c r="L4" t="inlineStr">
@@ -4234,26 +4246,26 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="N4" s="1" t="n">
-        <v>0.2581</v>
-      </c>
-      <c r="O4" s="1" t="n">
-        <v>0.4318</v>
+      <c r="N4" s="2" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0.4471</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.258±0.432</t>
+          <t>0.355±0.447</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>[0.151, 0.366]</t>
-        </is>
-      </c>
-      <c r="R4" s="1" t="n">
+          <t>[0.244, 0.466]</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="S4" s="1" t="n">
+      <c r="S4" s="2" t="n">
         <v>0.503</v>
       </c>
       <c r="T4" t="inlineStr">
@@ -4266,10 +4278,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="V4" s="1" t="n">
+      <c r="V4" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="W4" s="1" t="n">
+      <c r="W4" s="2" t="n">
         <v>0.503</v>
       </c>
       <c r="X4" t="inlineStr">
@@ -4282,20 +4294,20 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="Z4" s="1" t="n">
-        <v>0.7258</v>
-      </c>
-      <c r="AA4" s="1" t="n">
+      <c r="Z4" s="2" t="n">
+        <v>0.8226</v>
+      </c>
+      <c r="AA4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AB4" s="1" t="n">
-        <v>0.4848</v>
-      </c>
-      <c r="AC4" s="1" t="n">
-        <v>0.6304</v>
-      </c>
-      <c r="AD4" s="1" t="n">
-        <v>0.7733</v>
+      <c r="AB4" s="2" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="AC4" s="2" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="AD4" s="2" t="n">
+        <v>0.8406</v>
       </c>
     </row>
     <row r="5">
@@ -4322,58 +4334,58 @@
       <c r="E5" t="n">
         <v>62</v>
       </c>
-      <c r="F5" s="1" t="n">
-        <v>0.746</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>0.4282</v>
+      <c r="F5" s="2" t="n">
+        <v>0.8145</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.2966</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.746±0.428</t>
+          <t>0.815±0.297</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[0.639, 0.853]</t>
-        </is>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>0.4597</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>0.4963</v>
+          <t>[0.741, 0.888]</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0.4637</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0.4997</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.460±0.496</t>
+          <t>0.464±0.500</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>[0.336, 0.583]</t>
-        </is>
-      </c>
-      <c r="N5" s="1" t="n">
-        <v>0.2863</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>0.4523</v>
+          <t>[0.339, 0.588]</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0.4111</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.286±0.452</t>
+          <t>0.351±0.411</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>[0.174, 0.399]</t>
-        </is>
-      </c>
-      <c r="R5" s="1" t="n">
+          <t>[0.248, 0.453]</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="S5" s="1" t="n">
+      <c r="S5" s="2" t="n">
         <v>0.503</v>
       </c>
       <c r="T5" t="inlineStr">
@@ -4386,36 +4398,36 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="V5" s="1" t="n">
-        <v>0.4631</v>
-      </c>
-      <c r="W5" s="1" t="n">
-        <v>0.4987</v>
+      <c r="V5" s="2" t="n">
+        <v>0.4654</v>
+      </c>
+      <c r="W5" s="2" t="n">
+        <v>0.5009</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.463±0.499</t>
+          <t>0.465±0.501</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>[0.339, 0.587]</t>
-        </is>
-      </c>
-      <c r="Z5" s="1" t="n">
-        <v>0.746</v>
-      </c>
-      <c r="AA5" s="1" t="n">
-        <v>0.9828</v>
-      </c>
-      <c r="AB5" s="1" t="n">
-        <v>0.5379</v>
-      </c>
-      <c r="AC5" s="1" t="n">
-        <v>0.6514</v>
-      </c>
-      <c r="AD5" s="1" t="n">
-        <v>0.7835</v>
+          <t>[0.341, 0.590]</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>0.8145</v>
+      </c>
+      <c r="AA5" s="2" t="n">
+        <v>0.9913999999999999</v>
+      </c>
+      <c r="AB5" s="2" t="n">
+        <v>0.6591</v>
+      </c>
+      <c r="AC5" s="2" t="n">
+        <v>0.7188</v>
+      </c>
+      <c r="AD5" s="2" t="n">
+        <v>0.8333</v>
       </c>
     </row>
     <row r="6">
@@ -4442,26 +4454,26 @@
       <c r="E6" t="n">
         <v>62</v>
       </c>
-      <c r="F6" s="1" t="n">
-        <v>0.7661</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>0.4121</v>
+      <c r="F6" s="2" t="n">
+        <v>0.7823</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.3907</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.766±0.412</t>
+          <t>0.782±0.391</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[0.664, 0.869]</t>
-        </is>
-      </c>
-      <c r="J6" s="1" t="n">
+          <t>[0.685, 0.880]</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="K6" s="1" t="n">
+      <c r="K6" s="2" t="n">
         <v>0.503</v>
       </c>
       <c r="L6" t="inlineStr">
@@ -4474,26 +4486,26 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="N6" s="1" t="n">
-        <v>0.2984</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <v>0.4478</v>
+      <c r="N6" s="2" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0.4457</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.298±0.448</t>
+          <t>0.315±0.446</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>[0.187, 0.410]</t>
-        </is>
-      </c>
-      <c r="R6" s="1" t="n">
+          <t>[0.204, 0.425]</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="S6" s="1" t="n">
+      <c r="S6" s="2" t="n">
         <v>0.503</v>
       </c>
       <c r="T6" t="inlineStr">
@@ -4506,10 +4518,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="V6" s="1" t="n">
+      <c r="V6" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="W6" s="1" t="n">
+      <c r="W6" s="2" t="n">
         <v>0.503</v>
       </c>
       <c r="X6" t="inlineStr">
@@ -4522,20 +4534,20 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="Z6" s="1" t="n">
-        <v>0.7661</v>
-      </c>
-      <c r="AA6" s="1" t="n">
+      <c r="Z6" s="2" t="n">
+        <v>0.7823</v>
+      </c>
+      <c r="AA6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AB6" s="1" t="n">
-        <v>0.5606</v>
-      </c>
-      <c r="AC6" s="1" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="AD6" s="1" t="n">
-        <v>0.8</v>
+      <c r="AB6" s="2" t="n">
+        <v>0.5909</v>
+      </c>
+      <c r="AC6" s="2" t="n">
+        <v>0.6824</v>
+      </c>
+      <c r="AD6" s="2" t="n">
+        <v>0.8112</v>
       </c>
     </row>
     <row r="7">
@@ -4562,58 +4574,58 @@
       <c r="E7" t="n">
         <v>62</v>
       </c>
-      <c r="F7" s="1" t="n">
-        <v>0.7379</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>0.4328</v>
+      <c r="F7" s="2" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.3521</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.738±0.433</t>
+          <t>0.754±0.352</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[0.630, 0.846]</t>
-        </is>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>0.4637</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>0.4997</v>
+          <t>[0.666, 0.842]</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.4516</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0.4914</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.464±0.500</t>
+          <t>0.452±0.491</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>[0.339, 0.588]</t>
-        </is>
-      </c>
-      <c r="N7" s="1" t="n">
-        <v>0.2742</v>
-      </c>
-      <c r="O7" s="1" t="n">
-        <v>0.4429</v>
+          <t>[0.329, 0.574]</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0.4001</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.274±0.443</t>
+          <t>0.302±0.400</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>[0.164, 0.384]</t>
-        </is>
-      </c>
-      <c r="R7" s="1" t="n">
+          <t>[0.203, 0.402]</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="S7" s="1" t="n">
+      <c r="S7" s="2" t="n">
         <v>0.503</v>
       </c>
       <c r="T7" t="inlineStr">
@@ -4626,36 +4638,36 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="V7" s="1" t="n">
-        <v>0.4654</v>
-      </c>
-      <c r="W7" s="1" t="n">
-        <v>0.5009</v>
+      <c r="V7" s="2" t="n">
+        <v>0.4578</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0.4946</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.465±0.501</t>
+          <t>0.458±0.495</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>[0.341, 0.590]</t>
-        </is>
-      </c>
-      <c r="Z7" s="1" t="n">
-        <v>0.7379</v>
-      </c>
-      <c r="AA7" s="1" t="n">
-        <v>0.9913999999999999</v>
-      </c>
-      <c r="AB7" s="1" t="n">
-        <v>0.5152</v>
-      </c>
-      <c r="AC7" s="1" t="n">
-        <v>0.6425</v>
-      </c>
-      <c r="AD7" s="1" t="n">
-        <v>0.7796999999999999</v>
+          <t>[0.335, 0.581]</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="AA7" s="2" t="n">
+        <v>0.9655</v>
+      </c>
+      <c r="AB7" s="2" t="n">
+        <v>0.5682</v>
+      </c>
+      <c r="AC7" s="2" t="n">
+        <v>0.6627</v>
+      </c>
+      <c r="AD7" s="2" t="n">
+        <v>0.786</v>
       </c>
     </row>
   </sheetData>

--- a/experiments/spatial_temporal_graph/experiment_metrics.xlsx
+++ b/experiments/spatial_temporal_graph/experiment_metrics.xlsx
@@ -24,16 +24,13 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -44,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -52,21 +49,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -454,77 +442,77 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>MaxTrials</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>N Folds/Subjects</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Acc Mean±SD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Sens Mean±SD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Spec Mean±SD</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Prec Mean±SD</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>F1 Mean±SD</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Overall Acc</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Overall Sens</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Overall Spec</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Overall Prec</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Overall F1</t>
         </is>
@@ -579,19 +567,19 @@
           <t>0.773±0.109</t>
         </is>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="1" t="n">
         <v>0.75</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" s="1" t="n">
         <v>0.8966</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M2" s="1" t="n">
         <v>0.6212</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" s="1" t="n">
         <v>0.6753</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="O2" s="1" t="n">
         <v>0.7704</v>
       </c>
     </row>
@@ -644,19 +632,19 @@
           <t>0.757±0.059</t>
         </is>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="1" t="n">
         <v>0.7339</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="L3" s="1" t="n">
         <v>0.8793</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="M3" s="1" t="n">
         <v>0.6061</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" s="1" t="n">
         <v>0.6623</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="O3" s="1" t="n">
         <v>0.7556</v>
       </c>
     </row>
@@ -709,19 +697,19 @@
           <t>0.777±0.097</t>
         </is>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="1" t="n">
         <v>0.7419</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L4" s="1" t="n">
         <v>0.931</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="M4" s="1" t="n">
         <v>0.5758</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" s="1" t="n">
         <v>0.6585</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="O4" s="1" t="n">
         <v>0.7714</v>
       </c>
     </row>
@@ -774,19 +762,19 @@
           <t>0.740±0.067</t>
         </is>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="1" t="n">
         <v>0.6935</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="L5" s="1" t="n">
         <v>0.931</v>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="M5" s="1" t="n">
         <v>0.4848</v>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N5" s="1" t="n">
         <v>0.6136</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="O5" s="1" t="n">
         <v>0.7397</v>
       </c>
     </row>
@@ -839,19 +827,19 @@
           <t>0.794±0.102</t>
         </is>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="1" t="n">
         <v>0.7742</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="L6" s="1" t="n">
         <v>0.9137999999999999</v>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="M6" s="1" t="n">
         <v>0.6515</v>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="N6" s="1" t="n">
         <v>0.6974</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="O6" s="1" t="n">
         <v>0.791</v>
       </c>
     </row>
@@ -904,19 +892,19 @@
           <t>0.750±0.073</t>
         </is>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="1" t="n">
         <v>0.7137</v>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="L7" s="1" t="n">
         <v>0.8966</v>
       </c>
-      <c r="M7" s="2" t="n">
+      <c r="M7" s="1" t="n">
         <v>0.553</v>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="N7" s="1" t="n">
         <v>0.638</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="O7" s="1" t="n">
         <v>0.7455000000000001</v>
       </c>
     </row>
@@ -967,152 +955,152 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>MaxTrials</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>N Folds/Subjects</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Acc Mean</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Acc SD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Acc Mean±SD</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Acc 95% CI</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Sens Mean</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Sens SD</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Sens Mean±SD</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Sens 95% CI</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Spec Mean</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Spec SD</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Spec Mean±SD</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Spec 95% CI</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Prec Mean</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Prec SD</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Prec Mean±SD</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Prec 95% CI</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>F1 Mean</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>F1 SD</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>F1 Mean±SD</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>F1 95% CI</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Overall Acc</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Overall Sens</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Overall Spec</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Overall Prec</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Overall F1</t>
         </is>
@@ -1142,10 +1130,10 @@
       <c r="E2" t="n">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="1" t="n">
         <v>0.7494</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="1" t="n">
         <v>0.1254</v>
       </c>
       <c r="H2" t="inlineStr">
@@ -1158,10 +1146,10 @@
           <t>[0.639, 0.859]</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" s="1" t="n">
         <v>0.9</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="1" t="n">
         <v>0.1369</v>
       </c>
       <c r="L2" t="inlineStr">
@@ -1174,10 +1162,10 @@
           <t>[0.780, 1.020]</t>
         </is>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" s="1" t="n">
         <v>0.631</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="O2" s="1" t="n">
         <v>0.2133</v>
       </c>
       <c r="P2" t="inlineStr">
@@ -1190,10 +1178,10 @@
           <t>[0.444, 0.818]</t>
         </is>
       </c>
-      <c r="R2" s="2" t="n">
+      <c r="R2" s="1" t="n">
         <v>0.6942</v>
       </c>
-      <c r="S2" s="2" t="n">
+      <c r="S2" s="1" t="n">
         <v>0.1487</v>
       </c>
       <c r="T2" t="inlineStr">
@@ -1206,10 +1194,10 @@
           <t>[0.564, 0.824]</t>
         </is>
       </c>
-      <c r="V2" s="2" t="n">
+      <c r="V2" s="1" t="n">
         <v>0.7727000000000001</v>
       </c>
-      <c r="W2" s="2" t="n">
+      <c r="W2" s="1" t="n">
         <v>0.109</v>
       </c>
       <c r="X2" t="inlineStr">
@@ -1222,19 +1210,19 @@
           <t>[0.677, 0.868]</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="n">
+      <c r="Z2" s="1" t="n">
         <v>0.75</v>
       </c>
-      <c r="AA2" s="2" t="n">
+      <c r="AA2" s="1" t="n">
         <v>0.8966</v>
       </c>
-      <c r="AB2" s="2" t="n">
+      <c r="AB2" s="1" t="n">
         <v>0.6212</v>
       </c>
-      <c r="AC2" s="2" t="n">
+      <c r="AC2" s="1" t="n">
         <v>0.6753</v>
       </c>
-      <c r="AD2" s="2" t="n">
+      <c r="AD2" s="1" t="n">
         <v>0.7704</v>
       </c>
     </row>
@@ -1262,10 +1250,10 @@
       <c r="E3" t="n">
         <v>5</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="1" t="n">
         <v>0.7327</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="1" t="n">
         <v>0.07729999999999999</v>
       </c>
       <c r="H3" t="inlineStr">
@@ -1278,10 +1266,10 @@
           <t>[0.665, 0.800]</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" s="1" t="n">
         <v>0.88</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="1" t="n">
         <v>0.0522</v>
       </c>
       <c r="L3" t="inlineStr">
@@ -1294,10 +1282,10 @@
           <t>[0.834, 0.926]</t>
         </is>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" s="1" t="n">
         <v>0.6083</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="O3" s="1" t="n">
         <v>0.1512</v>
       </c>
       <c r="P3" t="inlineStr">
@@ -1310,10 +1298,10 @@
           <t>[0.476, 0.741]</t>
         </is>
       </c>
-      <c r="R3" s="2" t="n">
+      <c r="R3" s="1" t="n">
         <v>0.6719000000000001</v>
       </c>
-      <c r="S3" s="2" t="n">
+      <c r="S3" s="1" t="n">
         <v>0.1022</v>
       </c>
       <c r="T3" t="inlineStr">
@@ -1326,10 +1314,10 @@
           <t>[0.582, 0.761]</t>
         </is>
       </c>
-      <c r="V3" s="2" t="n">
+      <c r="V3" s="1" t="n">
         <v>0.7568</v>
       </c>
-      <c r="W3" s="2" t="n">
+      <c r="W3" s="1" t="n">
         <v>0.0593</v>
       </c>
       <c r="X3" t="inlineStr">
@@ -1342,19 +1330,19 @@
           <t>[0.705, 0.809]</t>
         </is>
       </c>
-      <c r="Z3" s="2" t="n">
+      <c r="Z3" s="1" t="n">
         <v>0.7339</v>
       </c>
-      <c r="AA3" s="2" t="n">
+      <c r="AA3" s="1" t="n">
         <v>0.8793</v>
       </c>
-      <c r="AB3" s="2" t="n">
+      <c r="AB3" s="1" t="n">
         <v>0.6061</v>
       </c>
-      <c r="AC3" s="2" t="n">
+      <c r="AC3" s="1" t="n">
         <v>0.6623</v>
       </c>
-      <c r="AD3" s="2" t="n">
+      <c r="AD3" s="1" t="n">
         <v>0.7556</v>
       </c>
     </row>
@@ -1382,10 +1370,10 @@
       <c r="E4" t="n">
         <v>5</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="1" t="n">
         <v>0.741</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="1" t="n">
         <v>0.1276</v>
       </c>
       <c r="H4" t="inlineStr">
@@ -1398,10 +1386,10 @@
           <t>[0.629, 0.853]</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J4" s="1" t="n">
         <v>0.93</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="1" t="n">
         <v>0.0711</v>
       </c>
       <c r="L4" t="inlineStr">
@@ -1414,10 +1402,10 @@
           <t>[0.868, 0.992]</t>
         </is>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" s="1" t="n">
         <v>0.581</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="O4" s="1" t="n">
         <v>0.2525</v>
       </c>
       <c r="P4" t="inlineStr">
@@ -1430,10 +1418,10 @@
           <t>[0.360, 0.802]</t>
         </is>
       </c>
-      <c r="R4" s="2" t="n">
+      <c r="R4" s="1" t="n">
         <v>0.6842</v>
       </c>
-      <c r="S4" s="2" t="n">
+      <c r="S4" s="1" t="n">
         <v>0.1628</v>
       </c>
       <c r="T4" t="inlineStr">
@@ -1446,10 +1434,10 @@
           <t>[0.542, 0.827]</t>
         </is>
       </c>
-      <c r="V4" s="2" t="n">
+      <c r="V4" s="1" t="n">
         <v>0.7771</v>
       </c>
-      <c r="W4" s="2" t="n">
+      <c r="W4" s="1" t="n">
         <v>0.097</v>
       </c>
       <c r="X4" t="inlineStr">
@@ -1462,19 +1450,19 @@
           <t>[0.692, 0.862]</t>
         </is>
       </c>
-      <c r="Z4" s="2" t="n">
+      <c r="Z4" s="1" t="n">
         <v>0.7419</v>
       </c>
-      <c r="AA4" s="2" t="n">
+      <c r="AA4" s="1" t="n">
         <v>0.931</v>
       </c>
-      <c r="AB4" s="2" t="n">
+      <c r="AB4" s="1" t="n">
         <v>0.5758</v>
       </c>
-      <c r="AC4" s="2" t="n">
+      <c r="AC4" s="1" t="n">
         <v>0.6585</v>
       </c>
-      <c r="AD4" s="2" t="n">
+      <c r="AD4" s="1" t="n">
         <v>0.7714</v>
       </c>
     </row>
@@ -1502,10 +1490,10 @@
       <c r="E5" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="1" t="n">
         <v>0.6919999999999999</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="1" t="n">
         <v>0.0867</v>
       </c>
       <c r="H5" t="inlineStr">
@@ -1518,10 +1506,10 @@
           <t>[0.616, 0.768]</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="J5" s="1" t="n">
         <v>0.9317</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="1" t="n">
         <v>0.0551</v>
       </c>
       <c r="L5" t="inlineStr">
@@ -1534,10 +1522,10 @@
           <t>[0.883, 0.980]</t>
         </is>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N5" s="1" t="n">
         <v>0.4857</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="O5" s="1" t="n">
         <v>0.1236</v>
       </c>
       <c r="P5" t="inlineStr">
@@ -1550,10 +1538,10 @@
           <t>[0.377, 0.594]</t>
         </is>
       </c>
-      <c r="R5" s="2" t="n">
+      <c r="R5" s="1" t="n">
         <v>0.6169</v>
       </c>
-      <c r="S5" s="2" t="n">
+      <c r="S5" s="1" t="n">
         <v>0.07920000000000001</v>
       </c>
       <c r="T5" t="inlineStr">
@@ -1566,10 +1554,10 @@
           <t>[0.547, 0.686]</t>
         </is>
       </c>
-      <c r="V5" s="2" t="n">
+      <c r="V5" s="1" t="n">
         <v>0.7398</v>
       </c>
-      <c r="W5" s="2" t="n">
+      <c r="W5" s="1" t="n">
         <v>0.067</v>
       </c>
       <c r="X5" t="inlineStr">
@@ -1582,19 +1570,19 @@
           <t>[0.681, 0.798]</t>
         </is>
       </c>
-      <c r="Z5" s="2" t="n">
+      <c r="Z5" s="1" t="n">
         <v>0.6935</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AA5" s="1" t="n">
         <v>0.931</v>
       </c>
-      <c r="AB5" s="2" t="n">
+      <c r="AB5" s="1" t="n">
         <v>0.4848</v>
       </c>
-      <c r="AC5" s="2" t="n">
+      <c r="AC5" s="1" t="n">
         <v>0.6136</v>
       </c>
-      <c r="AD5" s="2" t="n">
+      <c r="AD5" s="1" t="n">
         <v>0.7397</v>
       </c>
     </row>
@@ -1622,10 +1610,10 @@
       <c r="E6" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="1" t="n">
         <v>0.7737000000000001</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="1" t="n">
         <v>0.1174</v>
       </c>
       <c r="H6" t="inlineStr">
@@ -1638,10 +1626,10 @@
           <t>[0.671, 0.877]</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="J6" s="1" t="n">
         <v>0.9133</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="1" t="n">
         <v>0.1023</v>
       </c>
       <c r="L6" t="inlineStr">
@@ -1654,10 +1642,10 @@
           <t>[0.824, 1.003]</t>
         </is>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="N6" s="1" t="n">
         <v>0.6595</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="O6" s="1" t="n">
         <v>0.2006</v>
       </c>
       <c r="P6" t="inlineStr">
@@ -1670,10 +1658,10 @@
           <t>[0.484, 0.835]</t>
         </is>
       </c>
-      <c r="R6" s="2" t="n">
+      <c r="R6" s="1" t="n">
         <v>0.7143</v>
       </c>
-      <c r="S6" s="2" t="n">
+      <c r="S6" s="1" t="n">
         <v>0.1457</v>
       </c>
       <c r="T6" t="inlineStr">
@@ -1686,10 +1674,10 @@
           <t>[0.587, 0.842]</t>
         </is>
       </c>
-      <c r="V6" s="2" t="n">
+      <c r="V6" s="1" t="n">
         <v>0.7936</v>
       </c>
-      <c r="W6" s="2" t="n">
+      <c r="W6" s="1" t="n">
         <v>0.1022</v>
       </c>
       <c r="X6" t="inlineStr">
@@ -1702,19 +1690,19 @@
           <t>[0.704, 0.883]</t>
         </is>
       </c>
-      <c r="Z6" s="2" t="n">
+      <c r="Z6" s="1" t="n">
         <v>0.7742</v>
       </c>
-      <c r="AA6" s="2" t="n">
+      <c r="AA6" s="1" t="n">
         <v>0.9137999999999999</v>
       </c>
-      <c r="AB6" s="2" t="n">
+      <c r="AB6" s="1" t="n">
         <v>0.6515</v>
       </c>
-      <c r="AC6" s="2" t="n">
+      <c r="AC6" s="1" t="n">
         <v>0.6974</v>
       </c>
-      <c r="AD6" s="2" t="n">
+      <c r="AD6" s="1" t="n">
         <v>0.791</v>
       </c>
     </row>
@@ -1742,10 +1730,10 @@
       <c r="E7" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="1" t="n">
         <v>0.7122000000000001</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="1" t="n">
         <v>0.1125</v>
       </c>
       <c r="H7" t="inlineStr">
@@ -1758,10 +1746,10 @@
           <t>[0.614, 0.811]</t>
         </is>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="J7" s="1" t="n">
         <v>0.9</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="1" t="n">
         <v>0.08119999999999999</v>
       </c>
       <c r="L7" t="inlineStr">
@@ -1774,10 +1762,10 @@
           <t>[0.829, 0.971]</t>
         </is>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="N7" s="1" t="n">
         <v>0.5583</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="O7" s="1" t="n">
         <v>0.2398</v>
       </c>
       <c r="P7" t="inlineStr">
@@ -1790,10 +1778,10 @@
           <t>[0.348, 0.769]</t>
         </is>
       </c>
-      <c r="R7" s="2" t="n">
+      <c r="R7" s="1" t="n">
         <v>0.6613</v>
       </c>
-      <c r="S7" s="2" t="n">
+      <c r="S7" s="1" t="n">
         <v>0.1403</v>
       </c>
       <c r="T7" t="inlineStr">
@@ -1806,10 +1794,10 @@
           <t>[0.538, 0.784]</t>
         </is>
       </c>
-      <c r="V7" s="2" t="n">
+      <c r="V7" s="1" t="n">
         <v>0.7504</v>
       </c>
-      <c r="W7" s="2" t="n">
+      <c r="W7" s="1" t="n">
         <v>0.0731</v>
       </c>
       <c r="X7" t="inlineStr">
@@ -1822,19 +1810,19 @@
           <t>[0.686, 0.815]</t>
         </is>
       </c>
-      <c r="Z7" s="2" t="n">
+      <c r="Z7" s="1" t="n">
         <v>0.7137</v>
       </c>
-      <c r="AA7" s="2" t="n">
+      <c r="AA7" s="1" t="n">
         <v>0.8966</v>
       </c>
-      <c r="AB7" s="2" t="n">
+      <c r="AB7" s="1" t="n">
         <v>0.553</v>
       </c>
-      <c r="AC7" s="2" t="n">
+      <c r="AC7" s="1" t="n">
         <v>0.638</v>
       </c>
-      <c r="AD7" s="2" t="n">
+      <c r="AD7" s="1" t="n">
         <v>0.7455000000000001</v>
       </c>
     </row>
@@ -1870,77 +1858,77 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>MaxTrials</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>N Folds/Subjects</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Acc Mean±SD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Sens Mean±SD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Spec Mean±SD</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Prec Mean±SD</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>F1 Mean±SD</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Overall Acc</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Overall Sens</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Overall Spec</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Overall Prec</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Overall F1</t>
         </is>
@@ -1995,19 +1983,19 @@
           <t>0.798±0.098</t>
         </is>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="1" t="n">
         <v>0.7661</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" s="1" t="n">
         <v>0.9483</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M2" s="1" t="n">
         <v>0.6061</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" s="1" t="n">
         <v>0.679</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="O2" s="1" t="n">
         <v>0.7914</v>
       </c>
     </row>
@@ -2060,19 +2048,19 @@
           <t>0.781±0.078</t>
         </is>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="1" t="n">
         <v>0.75</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="L3" s="1" t="n">
         <v>0.9137999999999999</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="M3" s="1" t="n">
         <v>0.6061</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" s="1" t="n">
         <v>0.6709000000000001</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="O3" s="1" t="n">
         <v>0.7737000000000001</v>
       </c>
     </row>
@@ -2125,19 +2113,19 @@
           <t>0.795±0.088</t>
         </is>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="1" t="n">
         <v>0.7661</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L4" s="1" t="n">
         <v>0.931</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="M4" s="1" t="n">
         <v>0.6212</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" s="1" t="n">
         <v>0.6835</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="O4" s="1" t="n">
         <v>0.7883</v>
       </c>
     </row>
@@ -2190,19 +2178,19 @@
           <t>0.775±0.080</t>
         </is>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="1" t="n">
         <v>0.7379</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="L5" s="1" t="n">
         <v>0.931</v>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="M5" s="1" t="n">
         <v>0.5682</v>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N5" s="1" t="n">
         <v>0.6545</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="O5" s="1" t="n">
         <v>0.7687</v>
       </c>
     </row>
@@ -2255,19 +2243,19 @@
           <t>0.805±0.113</t>
         </is>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="1" t="n">
         <v>0.7742</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="L6" s="1" t="n">
         <v>0.931</v>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="M6" s="1" t="n">
         <v>0.6364</v>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="N6" s="1" t="n">
         <v>0.6923</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="O6" s="1" t="n">
         <v>0.7941</v>
       </c>
     </row>
@@ -2320,19 +2308,19 @@
           <t>0.775±0.089</t>
         </is>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="1" t="n">
         <v>0.7419</v>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="L7" s="1" t="n">
         <v>0.8879</v>
       </c>
-      <c r="M7" s="2" t="n">
+      <c r="M7" s="1" t="n">
         <v>0.6136</v>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="N7" s="1" t="n">
         <v>0.6688</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="O7" s="1" t="n">
         <v>0.763</v>
       </c>
     </row>
@@ -2383,152 +2371,152 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>MaxTrials</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>N Folds/Subjects</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Acc Mean</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Acc SD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Acc Mean±SD</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Acc 95% CI</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Sens Mean</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Sens SD</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Sens Mean±SD</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Sens 95% CI</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Spec Mean</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Spec SD</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Spec Mean±SD</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Spec 95% CI</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Prec Mean</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Prec SD</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Prec Mean±SD</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Prec 95% CI</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>F1 Mean</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>F1 SD</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>F1 Mean±SD</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>F1 95% CI</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Overall Acc</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Overall Sens</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Overall Spec</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Overall Prec</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Overall F1</t>
         </is>
@@ -2558,10 +2546,10 @@
       <c r="E2" t="n">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="1" t="n">
         <v>0.7643</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="1" t="n">
         <v>0.1458</v>
       </c>
       <c r="H2" t="inlineStr">
@@ -2574,10 +2562,10 @@
           <t>[0.674, 0.855]</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" s="1" t="n">
         <v>0.9417</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="1" t="n">
         <v>0.09660000000000001</v>
       </c>
       <c r="L2" t="inlineStr">
@@ -2590,10 +2578,10 @@
           <t>[0.882, 1.002]</t>
         </is>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" s="1" t="n">
         <v>0.5917</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="O2" s="1" t="n">
         <v>0.3035</v>
       </c>
       <c r="P2" t="inlineStr">
@@ -2606,10 +2594,10 @@
           <t>[0.404, 0.780]</t>
         </is>
       </c>
-      <c r="R2" s="2" t="n">
+      <c r="R2" s="1" t="n">
         <v>0.7050999999999999</v>
       </c>
-      <c r="S2" s="2" t="n">
+      <c r="S2" s="1" t="n">
         <v>0.1377</v>
       </c>
       <c r="T2" t="inlineStr">
@@ -2622,10 +2610,10 @@
           <t>[0.620, 0.790]</t>
         </is>
       </c>
-      <c r="V2" s="2" t="n">
+      <c r="V2" s="1" t="n">
         <v>0.7977</v>
       </c>
-      <c r="W2" s="2" t="n">
+      <c r="W2" s="1" t="n">
         <v>0.0984</v>
       </c>
       <c r="X2" t="inlineStr">
@@ -2638,19 +2626,19 @@
           <t>[0.737, 0.859]</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="n">
+      <c r="Z2" s="1" t="n">
         <v>0.7661</v>
       </c>
-      <c r="AA2" s="2" t="n">
+      <c r="AA2" s="1" t="n">
         <v>0.9483</v>
       </c>
-      <c r="AB2" s="2" t="n">
+      <c r="AB2" s="1" t="n">
         <v>0.6061</v>
       </c>
-      <c r="AC2" s="2" t="n">
+      <c r="AC2" s="1" t="n">
         <v>0.679</v>
       </c>
-      <c r="AD2" s="2" t="n">
+      <c r="AD2" s="1" t="n">
         <v>0.7914</v>
       </c>
     </row>
@@ -2678,10 +2666,10 @@
       <c r="E3" t="n">
         <v>10</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="1" t="n">
         <v>0.7494</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="1" t="n">
         <v>0.1286</v>
       </c>
       <c r="H3" t="inlineStr">
@@ -2694,10 +2682,10 @@
           <t>[0.670, 0.829]</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" s="1" t="n">
         <v>0.9083</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="1" t="n">
         <v>0.0829</v>
       </c>
       <c r="L3" t="inlineStr">
@@ -2710,10 +2698,10 @@
           <t>[0.857, 0.960]</t>
         </is>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" s="1" t="n">
         <v>0.5917</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="O3" s="1" t="n">
         <v>0.2789</v>
       </c>
       <c r="P3" t="inlineStr">
@@ -2726,10 +2714,10 @@
           <t>[0.419, 0.765]</t>
         </is>
       </c>
-      <c r="R3" s="2" t="n">
+      <c r="R3" s="1" t="n">
         <v>0.6991000000000001</v>
       </c>
-      <c r="S3" s="2" t="n">
+      <c r="S3" s="1" t="n">
         <v>0.1272</v>
       </c>
       <c r="T3" t="inlineStr">
@@ -2742,10 +2730,10 @@
           <t>[0.620, 0.778]</t>
         </is>
       </c>
-      <c r="V3" s="2" t="n">
+      <c r="V3" s="1" t="n">
         <v>0.781</v>
       </c>
-      <c r="W3" s="2" t="n">
+      <c r="W3" s="1" t="n">
         <v>0.0784</v>
       </c>
       <c r="X3" t="inlineStr">
@@ -2758,19 +2746,19 @@
           <t>[0.732, 0.830]</t>
         </is>
       </c>
-      <c r="Z3" s="2" t="n">
+      <c r="Z3" s="1" t="n">
         <v>0.75</v>
       </c>
-      <c r="AA3" s="2" t="n">
+      <c r="AA3" s="1" t="n">
         <v>0.9137999999999999</v>
       </c>
-      <c r="AB3" s="2" t="n">
+      <c r="AB3" s="1" t="n">
         <v>0.6061</v>
       </c>
-      <c r="AC3" s="2" t="n">
+      <c r="AC3" s="1" t="n">
         <v>0.6709000000000001</v>
       </c>
-      <c r="AD3" s="2" t="n">
+      <c r="AD3" s="1" t="n">
         <v>0.7737000000000001</v>
       </c>
     </row>
@@ -2798,10 +2786,10 @@
       <c r="E4" t="n">
         <v>10</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="1" t="n">
         <v>0.7643</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="1" t="n">
         <v>0.1348</v>
       </c>
       <c r="H4" t="inlineStr">
@@ -2814,10 +2802,10 @@
           <t>[0.681, 0.848]</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J4" s="1" t="n">
         <v>0.9333</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="1" t="n">
         <v>0.0861</v>
       </c>
       <c r="L4" t="inlineStr">
@@ -2830,10 +2818,10 @@
           <t>[0.880, 0.987]</t>
         </is>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" s="1" t="n">
         <v>0.6083</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="O4" s="1" t="n">
         <v>0.2751</v>
       </c>
       <c r="P4" t="inlineStr">
@@ -2846,10 +2834,10 @@
           <t>[0.438, 0.779]</t>
         </is>
       </c>
-      <c r="R4" s="2" t="n">
+      <c r="R4" s="1" t="n">
         <v>0.7029</v>
       </c>
-      <c r="S4" s="2" t="n">
+      <c r="S4" s="1" t="n">
         <v>0.1212</v>
       </c>
       <c r="T4" t="inlineStr">
@@ -2862,10 +2850,10 @@
           <t>[0.628, 0.778]</t>
         </is>
       </c>
-      <c r="V4" s="2" t="n">
+      <c r="V4" s="1" t="n">
         <v>0.7951</v>
       </c>
-      <c r="W4" s="2" t="n">
+      <c r="W4" s="1" t="n">
         <v>0.08840000000000001</v>
       </c>
       <c r="X4" t="inlineStr">
@@ -2878,19 +2866,19 @@
           <t>[0.740, 0.850]</t>
         </is>
       </c>
-      <c r="Z4" s="2" t="n">
+      <c r="Z4" s="1" t="n">
         <v>0.7661</v>
       </c>
-      <c r="AA4" s="2" t="n">
+      <c r="AA4" s="1" t="n">
         <v>0.931</v>
       </c>
-      <c r="AB4" s="2" t="n">
+      <c r="AB4" s="1" t="n">
         <v>0.6212</v>
       </c>
-      <c r="AC4" s="2" t="n">
+      <c r="AC4" s="1" t="n">
         <v>0.6835</v>
       </c>
-      <c r="AD4" s="2" t="n">
+      <c r="AD4" s="1" t="n">
         <v>0.7883</v>
       </c>
     </row>
@@ -2918,10 +2906,10 @@
       <c r="E5" t="n">
         <v>10</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="1" t="n">
         <v>0.7363</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="1" t="n">
         <v>0.1327</v>
       </c>
       <c r="H5" t="inlineStr">
@@ -2934,10 +2922,10 @@
           <t>[0.654, 0.819]</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="J5" s="1" t="n">
         <v>0.9292</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="1" t="n">
         <v>0.0557</v>
       </c>
       <c r="L5" t="inlineStr">
@@ -2950,10 +2938,10 @@
           <t>[0.895, 0.964]</t>
         </is>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N5" s="1" t="n">
         <v>0.5563</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="O5" s="1" t="n">
         <v>0.2584</v>
       </c>
       <c r="P5" t="inlineStr">
@@ -2966,10 +2954,10 @@
           <t>[0.396, 0.716]</t>
         </is>
       </c>
-      <c r="R5" s="2" t="n">
+      <c r="R5" s="1" t="n">
         <v>0.6712</v>
       </c>
-      <c r="S5" s="2" t="n">
+      <c r="S5" s="1" t="n">
         <v>0.1048</v>
       </c>
       <c r="T5" t="inlineStr">
@@ -2982,10 +2970,10 @@
           <t>[0.606, 0.736]</t>
         </is>
       </c>
-      <c r="V5" s="2" t="n">
+      <c r="V5" s="1" t="n">
         <v>0.775</v>
       </c>
-      <c r="W5" s="2" t="n">
+      <c r="W5" s="1" t="n">
         <v>0.07969999999999999</v>
       </c>
       <c r="X5" t="inlineStr">
@@ -2998,19 +2986,19 @@
           <t>[0.726, 0.824]</t>
         </is>
       </c>
-      <c r="Z5" s="2" t="n">
+      <c r="Z5" s="1" t="n">
         <v>0.7379</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AA5" s="1" t="n">
         <v>0.931</v>
       </c>
-      <c r="AB5" s="2" t="n">
+      <c r="AB5" s="1" t="n">
         <v>0.5682</v>
       </c>
-      <c r="AC5" s="2" t="n">
+      <c r="AC5" s="1" t="n">
         <v>0.6545</v>
       </c>
-      <c r="AD5" s="2" t="n">
+      <c r="AD5" s="1" t="n">
         <v>0.7687</v>
       </c>
     </row>
@@ -3038,10 +3026,10 @@
       <c r="E6" t="n">
         <v>10</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="1" t="n">
         <v>0.7714</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="1" t="n">
         <v>0.1669</v>
       </c>
       <c r="H6" t="inlineStr">
@@ -3054,10 +3042,10 @@
           <t>[0.668, 0.875]</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="J6" s="1" t="n">
         <v>0.9333</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="1" t="n">
         <v>0.1165</v>
       </c>
       <c r="L6" t="inlineStr">
@@ -3070,10 +3058,10 @@
           <t>[0.861, 1.006]</t>
         </is>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="N6" s="1" t="n">
         <v>0.625</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="O6" s="1" t="n">
         <v>0.3481</v>
       </c>
       <c r="P6" t="inlineStr">
@@ -3086,10 +3074,10 @@
           <t>[0.409, 0.841]</t>
         </is>
       </c>
-      <c r="R6" s="2" t="n">
+      <c r="R6" s="1" t="n">
         <v>0.7363</v>
       </c>
-      <c r="S6" s="2" t="n">
+      <c r="S6" s="1" t="n">
         <v>0.1836</v>
       </c>
       <c r="T6" t="inlineStr">
@@ -3102,10 +3090,10 @@
           <t>[0.622, 0.850]</t>
         </is>
       </c>
-      <c r="V6" s="2" t="n">
+      <c r="V6" s="1" t="n">
         <v>0.8055</v>
       </c>
-      <c r="W6" s="2" t="n">
+      <c r="W6" s="1" t="n">
         <v>0.1132</v>
       </c>
       <c r="X6" t="inlineStr">
@@ -3118,19 +3106,19 @@
           <t>[0.735, 0.876]</t>
         </is>
       </c>
-      <c r="Z6" s="2" t="n">
+      <c r="Z6" s="1" t="n">
         <v>0.7742</v>
       </c>
-      <c r="AA6" s="2" t="n">
+      <c r="AA6" s="1" t="n">
         <v>0.931</v>
       </c>
-      <c r="AB6" s="2" t="n">
+      <c r="AB6" s="1" t="n">
         <v>0.6364</v>
       </c>
-      <c r="AC6" s="2" t="n">
+      <c r="AC6" s="1" t="n">
         <v>0.6923</v>
       </c>
-      <c r="AD6" s="2" t="n">
+      <c r="AD6" s="1" t="n">
         <v>0.7941</v>
       </c>
     </row>
@@ -3158,10 +3146,10 @@
       <c r="E7" t="n">
         <v>10</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="1" t="n">
         <v>0.7399</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="1" t="n">
         <v>0.1463</v>
       </c>
       <c r="H7" t="inlineStr">
@@ -3174,10 +3162,10 @@
           <t>[0.649, 0.831]</t>
         </is>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="J7" s="1" t="n">
         <v>0.8875</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="1" t="n">
         <v>0.0682</v>
       </c>
       <c r="L7" t="inlineStr">
@@ -3190,10 +3178,10 @@
           <t>[0.845, 0.930]</t>
         </is>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="N7" s="1" t="n">
         <v>0.5938</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="O7" s="1" t="n">
         <v>0.2992</v>
       </c>
       <c r="P7" t="inlineStr">
@@ -3206,10 +3194,10 @@
           <t>[0.408, 0.779]</t>
         </is>
       </c>
-      <c r="R7" s="2" t="n">
+      <c r="R7" s="1" t="n">
         <v>0.7005</v>
       </c>
-      <c r="S7" s="2" t="n">
+      <c r="S7" s="1" t="n">
         <v>0.1349</v>
       </c>
       <c r="T7" t="inlineStr">
@@ -3222,10 +3210,10 @@
           <t>[0.617, 0.784]</t>
         </is>
       </c>
-      <c r="V7" s="2" t="n">
+      <c r="V7" s="1" t="n">
         <v>0.7746</v>
       </c>
-      <c r="W7" s="2" t="n">
+      <c r="W7" s="1" t="n">
         <v>0.0886</v>
       </c>
       <c r="X7" t="inlineStr">
@@ -3238,19 +3226,19 @@
           <t>[0.720, 0.830]</t>
         </is>
       </c>
-      <c r="Z7" s="2" t="n">
+      <c r="Z7" s="1" t="n">
         <v>0.7419</v>
       </c>
-      <c r="AA7" s="2" t="n">
+      <c r="AA7" s="1" t="n">
         <v>0.8879</v>
       </c>
-      <c r="AB7" s="2" t="n">
+      <c r="AB7" s="1" t="n">
         <v>0.6136</v>
       </c>
-      <c r="AC7" s="2" t="n">
+      <c r="AC7" s="1" t="n">
         <v>0.6688</v>
       </c>
-      <c r="AD7" s="2" t="n">
+      <c r="AD7" s="1" t="n">
         <v>0.763</v>
       </c>
     </row>
@@ -3286,77 +3274,77 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>MaxTrials</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>N Folds/Subjects</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Acc Mean±SD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Sens Mean±SD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Spec Mean±SD</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Prec Mean±SD</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>F1 Mean±SD</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Overall Acc</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Overall Sens</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Overall Spec</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Overall Prec</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Overall F1</t>
         </is>
@@ -3411,19 +3399,19 @@
           <t>0.468±0.503</t>
         </is>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="1" t="n">
         <v>0.7903</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M2" s="1" t="n">
         <v>0.6061</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" s="1" t="n">
         <v>0.6905</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="O2" s="1" t="n">
         <v>0.8169</v>
       </c>
     </row>
@@ -3476,19 +3464,19 @@
           <t>0.465±0.501</t>
         </is>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="1" t="n">
         <v>0.7702</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="L3" s="1" t="n">
         <v>0.9913999999999999</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="M3" s="1" t="n">
         <v>0.5758</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" s="1" t="n">
         <v>0.6725</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="O3" s="1" t="n">
         <v>0.8014</v>
       </c>
     </row>
@@ -3541,19 +3529,19 @@
           <t>0.468±0.503</t>
         </is>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="1" t="n">
         <v>0.8226</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="M4" s="1" t="n">
         <v>0.6667</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" s="1" t="n">
         <v>0.725</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="O4" s="1" t="n">
         <v>0.8406</v>
       </c>
     </row>
@@ -3606,19 +3594,19 @@
           <t>0.465±0.501</t>
         </is>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="1" t="n">
         <v>0.8145</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="L5" s="1" t="n">
         <v>0.9913999999999999</v>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="M5" s="1" t="n">
         <v>0.6591</v>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N5" s="1" t="n">
         <v>0.7188</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="O5" s="1" t="n">
         <v>0.8333</v>
       </c>
     </row>
@@ -3671,19 +3659,19 @@
           <t>0.468±0.503</t>
         </is>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="1" t="n">
         <v>0.7823</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="L6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="M6" s="1" t="n">
         <v>0.5909</v>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="N6" s="1" t="n">
         <v>0.6824</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="O6" s="1" t="n">
         <v>0.8112</v>
       </c>
     </row>
@@ -3736,19 +3724,19 @@
           <t>0.458±0.495</t>
         </is>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="1" t="n">
         <v>0.754</v>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="L7" s="1" t="n">
         <v>0.9655</v>
       </c>
-      <c r="M7" s="2" t="n">
+      <c r="M7" s="1" t="n">
         <v>0.5682</v>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="N7" s="1" t="n">
         <v>0.6627</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="O7" s="1" t="n">
         <v>0.786</v>
       </c>
     </row>
@@ -3799,152 +3787,152 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>MaxTrials</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>N Folds/Subjects</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Acc Mean</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Acc SD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Acc Mean±SD</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Acc 95% CI</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Sens Mean</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Sens SD</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Sens Mean±SD</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Sens 95% CI</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Spec Mean</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Spec SD</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Spec Mean±SD</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Spec 95% CI</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Prec Mean</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Prec SD</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Prec Mean±SD</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Prec 95% CI</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>F1 Mean</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>F1 SD</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>F1 Mean±SD</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>F1 95% CI</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Overall Acc</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Overall Sens</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Overall Spec</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Overall Prec</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Overall F1</t>
         </is>
@@ -3974,10 +3962,10 @@
       <c r="E2" t="n">
         <v>62</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="1" t="n">
         <v>0.7903</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="1" t="n">
         <v>0.3793</v>
       </c>
       <c r="H2" t="inlineStr">
@@ -3990,10 +3978,10 @@
           <t>[0.696, 0.885]</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="L2" t="inlineStr">
@@ -4006,10 +3994,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" s="1" t="n">
         <v>0.3226</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="O2" s="1" t="n">
         <v>0.4444</v>
       </c>
       <c r="P2" t="inlineStr">
@@ -4022,10 +4010,10 @@
           <t>[0.212, 0.433]</t>
         </is>
       </c>
-      <c r="R2" s="2" t="n">
+      <c r="R2" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="S2" s="2" t="n">
+      <c r="S2" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="T2" t="inlineStr">
@@ -4038,10 +4026,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="V2" s="2" t="n">
+      <c r="V2" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="W2" s="2" t="n">
+      <c r="W2" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="X2" t="inlineStr">
@@ -4054,19 +4042,19 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="n">
+      <c r="Z2" s="1" t="n">
         <v>0.7903</v>
       </c>
-      <c r="AA2" s="2" t="n">
+      <c r="AA2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AB2" s="2" t="n">
+      <c r="AB2" s="1" t="n">
         <v>0.6061</v>
       </c>
-      <c r="AC2" s="2" t="n">
+      <c r="AC2" s="1" t="n">
         <v>0.6905</v>
       </c>
-      <c r="AD2" s="2" t="n">
+      <c r="AD2" s="1" t="n">
         <v>0.8169</v>
       </c>
     </row>
@@ -4094,10 +4082,10 @@
       <c r="E3" t="n">
         <v>62</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="1" t="n">
         <v>0.7702</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="1" t="n">
         <v>0.363</v>
       </c>
       <c r="H3" t="inlineStr">
@@ -4110,10 +4098,10 @@
           <t>[0.680, 0.861]</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" s="1" t="n">
         <v>0.4637</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="1" t="n">
         <v>0.4997</v>
       </c>
       <c r="L3" t="inlineStr">
@@ -4126,10 +4114,10 @@
           <t>[0.339, 0.588]</t>
         </is>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" s="1" t="n">
         <v>0.3065</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="O3" s="1" t="n">
         <v>0.4135</v>
       </c>
       <c r="P3" t="inlineStr">
@@ -4142,10 +4130,10 @@
           <t>[0.204, 0.409]</t>
         </is>
       </c>
-      <c r="R3" s="2" t="n">
+      <c r="R3" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="S3" s="2" t="n">
+      <c r="S3" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="T3" t="inlineStr">
@@ -4158,10 +4146,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="V3" s="2" t="n">
+      <c r="V3" s="1" t="n">
         <v>0.4654</v>
       </c>
-      <c r="W3" s="2" t="n">
+      <c r="W3" s="1" t="n">
         <v>0.5009</v>
       </c>
       <c r="X3" t="inlineStr">
@@ -4174,19 +4162,19 @@
           <t>[0.341, 0.590]</t>
         </is>
       </c>
-      <c r="Z3" s="2" t="n">
+      <c r="Z3" s="1" t="n">
         <v>0.7702</v>
       </c>
-      <c r="AA3" s="2" t="n">
+      <c r="AA3" s="1" t="n">
         <v>0.9913999999999999</v>
       </c>
-      <c r="AB3" s="2" t="n">
+      <c r="AB3" s="1" t="n">
         <v>0.5758</v>
       </c>
-      <c r="AC3" s="2" t="n">
+      <c r="AC3" s="1" t="n">
         <v>0.6725</v>
       </c>
-      <c r="AD3" s="2" t="n">
+      <c r="AD3" s="1" t="n">
         <v>0.8014</v>
       </c>
     </row>
@@ -4214,10 +4202,10 @@
       <c r="E4" t="n">
         <v>62</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="1" t="n">
         <v>0.8226</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="1" t="n">
         <v>0.3399</v>
       </c>
       <c r="H4" t="inlineStr">
@@ -4230,10 +4218,10 @@
           <t>[0.738, 0.907]</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J4" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="L4" t="inlineStr">
@@ -4246,10 +4234,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" s="1" t="n">
         <v>0.3548</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="O4" s="1" t="n">
         <v>0.4471</v>
       </c>
       <c r="P4" t="inlineStr">
@@ -4262,10 +4250,10 @@
           <t>[0.244, 0.466]</t>
         </is>
       </c>
-      <c r="R4" s="2" t="n">
+      <c r="R4" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="S4" s="2" t="n">
+      <c r="S4" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="T4" t="inlineStr">
@@ -4278,10 +4266,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="V4" s="2" t="n">
+      <c r="V4" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="W4" s="2" t="n">
+      <c r="W4" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="X4" t="inlineStr">
@@ -4294,19 +4282,19 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="Z4" s="2" t="n">
+      <c r="Z4" s="1" t="n">
         <v>0.8226</v>
       </c>
-      <c r="AA4" s="2" t="n">
+      <c r="AA4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AB4" s="2" t="n">
+      <c r="AB4" s="1" t="n">
         <v>0.6667</v>
       </c>
-      <c r="AC4" s="2" t="n">
+      <c r="AC4" s="1" t="n">
         <v>0.725</v>
       </c>
-      <c r="AD4" s="2" t="n">
+      <c r="AD4" s="1" t="n">
         <v>0.8406</v>
       </c>
     </row>
@@ -4334,10 +4322,10 @@
       <c r="E5" t="n">
         <v>62</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="1" t="n">
         <v>0.8145</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="1" t="n">
         <v>0.2966</v>
       </c>
       <c r="H5" t="inlineStr">
@@ -4350,10 +4338,10 @@
           <t>[0.741, 0.888]</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="J5" s="1" t="n">
         <v>0.4637</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="1" t="n">
         <v>0.4997</v>
       </c>
       <c r="L5" t="inlineStr">
@@ -4366,10 +4354,10 @@
           <t>[0.339, 0.588]</t>
         </is>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N5" s="1" t="n">
         <v>0.3508</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="O5" s="1" t="n">
         <v>0.4111</v>
       </c>
       <c r="P5" t="inlineStr">
@@ -4382,10 +4370,10 @@
           <t>[0.248, 0.453]</t>
         </is>
       </c>
-      <c r="R5" s="2" t="n">
+      <c r="R5" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="S5" s="2" t="n">
+      <c r="S5" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="T5" t="inlineStr">
@@ -4398,10 +4386,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="V5" s="2" t="n">
+      <c r="V5" s="1" t="n">
         <v>0.4654</v>
       </c>
-      <c r="W5" s="2" t="n">
+      <c r="W5" s="1" t="n">
         <v>0.5009</v>
       </c>
       <c r="X5" t="inlineStr">
@@ -4414,19 +4402,19 @@
           <t>[0.341, 0.590]</t>
         </is>
       </c>
-      <c r="Z5" s="2" t="n">
+      <c r="Z5" s="1" t="n">
         <v>0.8145</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AA5" s="1" t="n">
         <v>0.9913999999999999</v>
       </c>
-      <c r="AB5" s="2" t="n">
+      <c r="AB5" s="1" t="n">
         <v>0.6591</v>
       </c>
-      <c r="AC5" s="2" t="n">
+      <c r="AC5" s="1" t="n">
         <v>0.7188</v>
       </c>
-      <c r="AD5" s="2" t="n">
+      <c r="AD5" s="1" t="n">
         <v>0.8333</v>
       </c>
     </row>
@@ -4454,10 +4442,10 @@
       <c r="E6" t="n">
         <v>62</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="1" t="n">
         <v>0.7823</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="1" t="n">
         <v>0.3907</v>
       </c>
       <c r="H6" t="inlineStr">
@@ -4470,10 +4458,10 @@
           <t>[0.685, 0.880]</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="J6" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="L6" t="inlineStr">
@@ -4486,10 +4474,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="N6" s="1" t="n">
         <v>0.3145</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="O6" s="1" t="n">
         <v>0.4457</v>
       </c>
       <c r="P6" t="inlineStr">
@@ -4502,10 +4490,10 @@
           <t>[0.204, 0.425]</t>
         </is>
       </c>
-      <c r="R6" s="2" t="n">
+      <c r="R6" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="S6" s="2" t="n">
+      <c r="S6" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="T6" t="inlineStr">
@@ -4518,10 +4506,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="V6" s="2" t="n">
+      <c r="V6" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="W6" s="2" t="n">
+      <c r="W6" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="X6" t="inlineStr">
@@ -4534,19 +4522,19 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="Z6" s="2" t="n">
+      <c r="Z6" s="1" t="n">
         <v>0.7823</v>
       </c>
-      <c r="AA6" s="2" t="n">
+      <c r="AA6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AB6" s="2" t="n">
+      <c r="AB6" s="1" t="n">
         <v>0.5909</v>
       </c>
-      <c r="AC6" s="2" t="n">
+      <c r="AC6" s="1" t="n">
         <v>0.6824</v>
       </c>
-      <c r="AD6" s="2" t="n">
+      <c r="AD6" s="1" t="n">
         <v>0.8112</v>
       </c>
     </row>
@@ -4574,10 +4562,10 @@
       <c r="E7" t="n">
         <v>62</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="1" t="n">
         <v>0.754</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="1" t="n">
         <v>0.3521</v>
       </c>
       <c r="H7" t="inlineStr">
@@ -4590,10 +4578,10 @@
           <t>[0.666, 0.842]</t>
         </is>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="J7" s="1" t="n">
         <v>0.4516</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="1" t="n">
         <v>0.4914</v>
       </c>
       <c r="L7" t="inlineStr">
@@ -4606,10 +4594,10 @@
           <t>[0.329, 0.574]</t>
         </is>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="N7" s="1" t="n">
         <v>0.3024</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="O7" s="1" t="n">
         <v>0.4001</v>
       </c>
       <c r="P7" t="inlineStr">
@@ -4622,10 +4610,10 @@
           <t>[0.203, 0.402]</t>
         </is>
       </c>
-      <c r="R7" s="2" t="n">
+      <c r="R7" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="S7" s="2" t="n">
+      <c r="S7" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="T7" t="inlineStr">
@@ -4638,10 +4626,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="V7" s="2" t="n">
+      <c r="V7" s="1" t="n">
         <v>0.4578</v>
       </c>
-      <c r="W7" s="2" t="n">
+      <c r="W7" s="1" t="n">
         <v>0.4946</v>
       </c>
       <c r="X7" t="inlineStr">
@@ -4654,19 +4642,19 @@
           <t>[0.335, 0.581]</t>
         </is>
       </c>
-      <c r="Z7" s="2" t="n">
+      <c r="Z7" s="1" t="n">
         <v>0.754</v>
       </c>
-      <c r="AA7" s="2" t="n">
+      <c r="AA7" s="1" t="n">
         <v>0.9655</v>
       </c>
-      <c r="AB7" s="2" t="n">
+      <c r="AB7" s="1" t="n">
         <v>0.5682</v>
       </c>
-      <c r="AC7" s="2" t="n">
+      <c r="AC7" s="1" t="n">
         <v>0.6627</v>
       </c>
-      <c r="AD7" s="2" t="n">
+      <c r="AD7" s="1" t="n">
         <v>0.786</v>
       </c>
     </row>
